--- a/02-Referencias/outros/resumo_fatura_fechamento_padrao.xlsx
+++ b/02-Referencias/outros/resumo_fatura_fechamento_padrao.xlsx
@@ -54,11 +54,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI267"/>
+  <dimension ref="A1:AI271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,17 +676,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>7.5.20</t>
+          <t>7.5.3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>TELECOMUNICAÇÕES</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>7.5.20 INTERNET</t>
+          <t>7.5.3 TELECOMUNICAÇÕES</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -707,16 +708,14 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000000 | [GIULIANA] EMBRATEL CLOUD OFFICE 365 05/2026 - S/NF - R$ 58,69 - VENCIMENTO EM 25/05/2026-PAGAMENTO VIA BOLETO BANCARIO--O NUMERO INFORMADO, É O NUMERO DA FATURA NO DOCUMENTO</t>
+          <t>REFERENTE A NF 000000000</t>
         </is>
       </c>
       <c r="X2" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y2" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>46167</v>
@@ -838,16 +837,14 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000003 | PEDIDO(S) ASSOCIADO(S): [0030005338] Cristina - referente ao serviço do gesseiro que abriu o espaço para o marceneiro colocar estrutura do móvel e depois fechou .. vencimento 15/05 pagamento pix: 46007927000154 (ARCE GESSO) IMPOSTOS RETIDOS: ISSQN ($8,04) Valor total da nota $400 VALOR LÍQUIDO DA NOTA: $391,96</t>
+          <t>REFERENTE A NF 000000003</t>
         </is>
       </c>
       <c r="X3" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z3" s="3" t="n">
         <v>46157</v>
@@ -969,16 +966,14 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000005 | PEDIDO(S) ASSOCIADO(S): [0030005366] Referente a compra de CASTANHA P/ PORTAO DE ELEVACAO, no valor de R$1.500,00. Forma de pagamento pix, chave: 66235712000106</t>
+          <t>REFERENTE A NF 000000005</t>
         </is>
       </c>
       <c r="X4" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y4" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>46167</v>
@@ -1100,16 +1095,14 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000039 | PEDIDO(S) ASSOCIADO(S): [0030005333] Cristina - Referente a mão de obra da equipe de churrasco ( campanha mês do Serralheiro) realizado na data 30/04 NF 39 PIX 15/05</t>
+          <t>REFERENTE A NF 000000039</t>
         </is>
       </c>
       <c r="X5" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y5" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>46157</v>
@@ -1231,16 +1224,14 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000042 | PEDIDO(S) ASSOCIADO(S): [0030005342] Cristina - Referente a serviços de auditoria de estoque vencimento 15/05 Pagamento por pix: 55.599.387/0001-36</t>
+          <t>REFERENTE A NF 000000042</t>
         </is>
       </c>
       <c r="X6" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y6" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>46157</v>
@@ -1330,17 +1321,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>7.5.20</t>
+          <t>7.5.9</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>CONSULTORIA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>7.5.20 INTERNET</t>
+          <t>7.5.9 CONSULTORIA</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1362,16 +1353,14 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000107 | PEDIDO(S) ASSOCIADO(S): [0030005322] CRISTINA - REF. GESTAO DE TRAFEGO GOOGLE - COMP 04/2026 NFS 107 VENC 15.05.2026 TRANSFERENCIA PIX CHAVE CNPJ: 52.596.265/0001-06 BANCO: 461 ASAAS I.P S.A AG: 0001 C/C: 4727065-7</t>
+          <t>REFERENTE A NF 000000107</t>
         </is>
       </c>
       <c r="X7" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y7" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>46157</v>
@@ -1493,16 +1482,14 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000119 | PEDIDO(S) ASSOCIADO(S): [0030005352] Referente a prestação de serviços de administração de redes sociais e conteúdos de Abril a Setembro. nf 119 boleto 15/05</t>
+          <t>REFERENTE A NF 000000119</t>
         </is>
       </c>
       <c r="X8" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>46157</v>
@@ -1624,16 +1611,14 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000196 | PEDIDO(S) ASSOCIADO(S): [0030005321] Cristina- Referente ao serviço de apoio à pesquisa intitulado “Projeto Modelagem baseada em dados de venda via Chatbots, no valor de R$ 11.880,00 Chave Pix: fundacte@gmail.com Favorecido: Fundacte- Fundação de Ciência Tecnologia e Ensino Instituição Bancária: Pag Bank Código do banco : 290- PagSeguro Internet S/A • Agência:0001 • Conta corrente:43023904-6 • CNPJ: 00.395.519/0001-16 O referido projeto possui vigência no período de fevereiro a agosto de 2026, conforme acordado com o professor Cássio NF 196 (3/6) 15/05</t>
+          <t>REFERENTE A NF 000000196</t>
         </is>
       </c>
       <c r="X9" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y9" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>46160</v>
@@ -1723,17 +1708,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>7.5.6</t>
+          <t>7.5.9</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MANUTENÇÕES E REPAROS - ESTRUTURA ADMINISTRATIVA</t>
+          <t>CONSULTORIA</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7.5.6 MANUTENÇÕES E REPAROS - ESTRUTURA ADMINISTRATIVA</t>
+          <t>7.5.9 CONSULTORIA</t>
         </is>
       </c>
       <c r="R10" t="n">
@@ -1755,16 +1740,14 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000257 | PEDIDO(S) ASSOCIADO(S): [0030005367] Cristina- Referente a prestação de serviços do eletricista que fez a instalação elétrica da máquina de produzir tira raiada. Nf 257 - Pix cnpj: 43104416000162 25/05</t>
+          <t>REFERENTE A NF 000000257</t>
         </is>
       </c>
       <c r="X10" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y10" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>46167</v>
@@ -1886,18 +1869,18 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000310 | PEDIDO(S) ASSOCIADO(S): [0030005401]. (GIULIANA) NFS 310, VENCIMENTO 15/06/2026, PAGAMENTO VIA BOLETO BANCÁRIO. HONORÁRIO CONTÁBIL REF. AO MÊS 05/2026.</t>
+          <t>REFERENTE A NF 000000310</t>
         </is>
       </c>
       <c r="X11" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>15/06/26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Y11" s="4" t="n">
+        <v>46188</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>46188</v>
+      </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
@@ -2015,16 +1998,14 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000388 | PEDIDO(S) ASSOCIADO(S): [0030005341] Cristina - Referente a prestação de serviço de comunicação da Band Fm PERIODO DE VEICULACAO: 20/04/2026 A 15/05/2026 VEICULACAO DE 100 COMERCIAIS DE 30". NF 388 Boleto 18/05</t>
+          <t>REFERENTE A NF 000000388</t>
         </is>
       </c>
       <c r="X12" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>46160</v>
@@ -2146,16 +2127,14 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000428 | PEDIDO(S) ASSOCIADO(S): [0030005324] CRISTINA - REF. A COMPRA DE PÃO - NF 428 TRANSFERENCIA PIX 05240771000170 José Carlos Ignácio Presidente Prudente ME 15/05</t>
+          <t>REFERENTE A NF 000000428</t>
         </is>
       </c>
       <c r="X13" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>46157</v>
@@ -2277,16 +2256,14 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000500 | PEDIDO(S) ASSOCIADO(S): [0030005389]</t>
+          <t>REFERENTE A NF 000000500</t>
         </is>
       </c>
       <c r="X14" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>17/06/26</t>
-        </is>
+      <c r="Y14" s="4" t="n">
+        <v>46190</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
@@ -2404,19 +2381,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000989 | PEDIDO(S) ASSOCIADO(S): [0030005339] Cristina - Referente a compra de materiais de limpeza para reabastecimento de estoque. NF 989 BOLETO 05/06</t>
+          <t>REFERENTE A NF 000000989</t>
         </is>
       </c>
       <c r="X15" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>05/06/26</t>
-        </is>
+      <c r="Y15" s="4" t="n">
+        <v>46178</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
@@ -2535,16 +2510,14 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000001464 | PEDIDO(S) ASSOCIADO(S): [0030005328] Cristina - Referente a itens de chope para utilizar no churrasco realizado 30/04 prestigiando ao dia do serralheiro para colaboradores e clientes. nf 1464 boleto 14/05</t>
+          <t>REFERENTE A NF 000001464</t>
         </is>
       </c>
       <c r="X16" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>14/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>46156</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>46156</v>
@@ -2666,16 +2639,14 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000164 | PEDIDO(S) ASSOCIADO(S): [0030005315]</t>
+          <t>REFERENTE A NF 000000164</t>
         </is>
       </c>
       <c r="X17" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>46171</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>46171</v>
@@ -2797,16 +2768,14 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000164 | PEDIDO(S) ASSOCIADO(S): [0030005315]</t>
+          <t>REFERENTE A NF 000000164</t>
         </is>
       </c>
       <c r="X18" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>28/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>46201</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -2926,16 +2895,14 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000001739 | PEDIDO(S) ASSOCIADO(S): [0030005332] Cristina - Referente a manutenção da polia eura 13 do pátio Braçofer. NF 1739 PIX 15/05 10.337.097/0001-86</t>
+          <t>REFERENTE A NF 000001739</t>
         </is>
       </c>
       <c r="X19" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y19" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>46157</v>
@@ -3057,16 +3024,14 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000003663 | PEDIDO(S) ASSOCIADO(S): [0030005345] Cristina - Referente a compra de alimentos para o churrasco em comemoração ao dia do serralheiro. Realizado em 30/04. Nf 3663 Boleto 15/05</t>
+          <t>REFERENTE A NF 000003663</t>
         </is>
       </c>
       <c r="X20" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>46157</v>
@@ -3188,16 +3153,14 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062227 | PEDIDO(S) ASSOCIADO(S): [0030005336]</t>
+          <t>REFERENTE A NF 000062227</t>
         </is>
       </c>
       <c r="X21" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>46171</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>46171</v>
@@ -3319,18 +3282,18 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062227 | PEDIDO(S) ASSOCIADO(S): [0030005336]</t>
+          <t>REFERENTE A NF 000062227</t>
         </is>
       </c>
       <c r="X22" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>16/06/26</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr"/>
+        <v>46143</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>46189</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>46189</v>
+      </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
@@ -3448,16 +3411,14 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062227 | PEDIDO(S) ASSOCIADO(S): [0030005336]</t>
+          <t>REFERENTE A NF 000062227</t>
         </is>
       </c>
       <c r="X23" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>29/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>46202</v>
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -3577,16 +3538,14 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062228 | PEDIDO(S) ASSOCIADO(S): [0030005335]</t>
+          <t>REFERENTE A NF 000062228</t>
         </is>
       </c>
       <c r="X24" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>46171</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>46171</v>
@@ -3708,18 +3667,18 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062228 | PEDIDO(S) ASSOCIADO(S): [0030005335]</t>
+          <t>REFERENTE A NF 000062228</t>
         </is>
       </c>
       <c r="X25" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>16/06/26</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr"/>
+        <v>46143</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>46189</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>46189</v>
+      </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
@@ -3837,16 +3796,14 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062228 | PEDIDO(S) ASSOCIADO(S): [0030005335]</t>
+          <t>REFERENTE A NF 000062228</t>
         </is>
       </c>
       <c r="X26" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>29/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y26" s="4" t="n">
+        <v>46202</v>
       </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -3966,19 +3923,17 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062529 | PEDIDO(S) ASSOCIADO(S): [0030005355]</t>
+          <t>REFERENTE A NF 000062529</t>
         </is>
       </c>
       <c r="X27" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>08/06/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>46181</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
@@ -4097,16 +4052,14 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062529 | PEDIDO(S) ASSOCIADO(S): [0030005355]</t>
+          <t>REFERENTE A NF 000062529</t>
         </is>
       </c>
       <c r="X28" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>22/06/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y28" s="4" t="n">
+        <v>46195</v>
       </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -4226,16 +4179,14 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062529 | PEDIDO(S) ASSOCIADO(S): [0030005355]</t>
+          <t>REFERENTE A NF 000062529</t>
         </is>
       </c>
       <c r="X29" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>07/07/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>46210</v>
       </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -4355,18 +4306,18 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062583 | PEDIDO(S) ASSOCIADO(S): [0030005356]</t>
+          <t>REFERENTE A NF 000062583</t>
         </is>
       </c>
       <c r="X30" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>10/06/26</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr"/>
+        <v>46153</v>
+      </c>
+      <c r="Y30" s="4" t="n">
+        <v>46183</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>46183</v>
+      </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr">
         <is>
@@ -4484,16 +4435,14 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062583 | PEDIDO(S) ASSOCIADO(S): [0030005356]</t>
+          <t>REFERENTE A NF 000062583</t>
         </is>
       </c>
       <c r="X31" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y31" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -4613,16 +4562,14 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000062583 | PEDIDO(S) ASSOCIADO(S): [0030005356]</t>
+          <t>REFERENTE A NF 000062583</t>
         </is>
       </c>
       <c r="X32" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>10/07/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>46213</v>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -4742,16 +4689,14 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000063224 | PEDIDO(S) ASSOCIADO(S): [0030005407]</t>
+          <t>REFERENTE A NF 000063224</t>
         </is>
       </c>
       <c r="X33" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>29/06/26</t>
-        </is>
+      <c r="Y33" s="4" t="n">
+        <v>46202</v>
       </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -4871,16 +4816,14 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000063224 | PEDIDO(S) ASSOCIADO(S): [0030005407]</t>
+          <t>REFERENTE A NF 000063224</t>
         </is>
       </c>
       <c r="X34" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>13/07/26</t>
-        </is>
+      <c r="Y34" s="4" t="n">
+        <v>46216</v>
       </c>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -5000,16 +4943,14 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000063224 | PEDIDO(S) ASSOCIADO(S): [0030005407]</t>
+          <t>REFERENTE A NF 000063224</t>
         </is>
       </c>
       <c r="X35" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>27/07/26</t>
-        </is>
+      <c r="Y35" s="4" t="n">
+        <v>46230</v>
       </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -5129,16 +5070,14 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009460 | PEDIDO(S) ASSOCIADO(S): [0030005350]</t>
+          <t>REFERENTE A NF 000009460</t>
         </is>
       </c>
       <c r="X36" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y36" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>46168</v>
@@ -5260,18 +5199,18 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009460 | PEDIDO(S) ASSOCIADO(S): [0030005350]</t>
+          <t>REFERENTE A NF 000009460</t>
         </is>
       </c>
       <c r="X37" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>10/06/26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr"/>
+        <v>46153</v>
+      </c>
+      <c r="Y37" s="4" t="n">
+        <v>46183</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46183</v>
+      </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr">
         <is>
@@ -5389,16 +5328,14 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009460 | PEDIDO(S) ASSOCIADO(S): [0030005350]</t>
+          <t>REFERENTE A NF 000009460</t>
         </is>
       </c>
       <c r="X38" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -5518,18 +5455,18 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009461 | PEDIDO(S) ASSOCIADO(S): [0030005390]</t>
+          <t>REFERENTE A NF 000009461</t>
         </is>
       </c>
       <c r="X39" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>11/06/26</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Y39" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>46184</v>
+      </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr">
         <is>
@@ -5647,16 +5584,14 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009461 | PEDIDO(S) ASSOCIADO(S): [0030005390]</t>
+          <t>REFERENTE A NF 000009461</t>
         </is>
       </c>
       <c r="X40" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>26/06/26</t>
-        </is>
+      <c r="Y40" s="4" t="n">
+        <v>46199</v>
       </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -5776,16 +5711,14 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009461 | PEDIDO(S) ASSOCIADO(S): [0030005390]</t>
+          <t>REFERENTE A NF 000009461</t>
         </is>
       </c>
       <c r="X41" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>11/07/26</t>
-        </is>
+      <c r="Y41" s="4" t="n">
+        <v>46214</v>
       </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
@@ -5905,18 +5838,18 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009462 | PEDIDO(S) ASSOCIADO(S): [0030005391]</t>
+          <t>REFERENTE A NF 000009462</t>
         </is>
       </c>
       <c r="X42" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>11/06/26</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Y42" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>46184</v>
+      </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr">
         <is>
@@ -6034,16 +5967,14 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009462 | PEDIDO(S) ASSOCIADO(S): [0030005391]</t>
+          <t>REFERENTE A NF 000009462</t>
         </is>
       </c>
       <c r="X43" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>26/06/26</t>
-        </is>
+      <c r="Y43" s="4" t="n">
+        <v>46199</v>
       </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
@@ -6163,16 +6094,14 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000009462 | PEDIDO(S) ASSOCIADO(S): [0030005391]</t>
+          <t>REFERENTE A NF 000009462</t>
         </is>
       </c>
       <c r="X44" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>11/07/26</t>
-        </is>
+      <c r="Y44" s="4" t="n">
+        <v>46214</v>
       </c>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
@@ -6290,16 +6219,14 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000012979 | PEDIDO(S) ASSOCIADO(S): [0030005346] Cristina - Referente a serviço de telefonia NF 12979 Boleto 25/05</t>
+          <t>REFERENTE A NF 000012979</t>
         </is>
       </c>
       <c r="X45" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y45" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>46167</v>
@@ -6421,16 +6348,14 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000016193 | PEDIDO(S) ASSOCIADO(S): [0030005323] Cristina - Referente a Hospedagem de Cristiano para a contagem de materiais do estoque no pátio HOSPEDE: CRISTIANO DA SILVA CHECK-IN: 30/04/2026 CHECK-OUT: 03/05/2026 nf 16193 boleto 26/05</t>
+          <t>REFERENTE A NF 000016193</t>
         </is>
       </c>
       <c r="X46" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+      <c r="Y46" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>46168</v>
@@ -6552,16 +6477,14 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000028472 | CRISTINA - REF EXAMES MEDICOS ADMISSIONAIS FUNCIONARIOS ALAN, CARLOS E LUCAS COMP ABRIL 2026. NF 28472 PAGTO VIA BOLETO BANCARIO PARA 15/05/2026.</t>
+          <t>REFERENTE A NF 000028472</t>
         </is>
       </c>
       <c r="X47" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y47" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z47" s="3" t="n">
         <v>46157</v>
@@ -6651,17 +6574,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>7.5.9</t>
+          <t>7.3.6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONSULTORIA</t>
+          <t>PLANO DE SAÚDE</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>7.5.9 CONSULTORIA</t>
+          <t>7.3.6 PLANO DE SAÚDE</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -6683,16 +6606,14 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029804 | CRISTINA - REF CONSULTORIA MENSAL DE SEGURANÇA DO TRABALHO COMP MAIO 2026. NF 29804 PAGTO VIA BOLETO BANCARIO PARA 15/05/2026. (VALOR LIQUIDO 281,28)</t>
+          <t>REFERENTE A NF 000029804</t>
         </is>
       </c>
       <c r="X48" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y48" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z48" s="3" t="n">
         <v>46157</v>
@@ -6814,19 +6735,17 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000456961 | PEDIDO(S) ASSOCIADO(S): [0030005348]</t>
+          <t>REFERENTE A NF 000456961</t>
         </is>
       </c>
       <c r="X49" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>07/06/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y49" s="4" t="n">
+        <v>46180</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr">
@@ -6945,16 +6864,14 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000456961 | PEDIDO(S) ASSOCIADO(S): [0030005348]</t>
+          <t>REFERENTE A NF 000456961</t>
         </is>
       </c>
       <c r="X50" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>22/06/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y50" s="4" t="n">
+        <v>46195</v>
       </c>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
@@ -7074,16 +6991,14 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000456961 | PEDIDO(S) ASSOCIADO(S): [0030005348]</t>
+          <t>REFERENTE A NF 000456961</t>
         </is>
       </c>
       <c r="X51" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>07/07/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y51" s="4" t="n">
+        <v>46210</v>
       </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
@@ -7203,16 +7118,14 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000457689 | PEDIDO(S) ASSOCIADO(S): [0030005383]</t>
+          <t>REFERENTE A NF 000457689</t>
         </is>
       </c>
       <c r="X52" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>20/06/26</t>
-        </is>
+      <c r="Y52" s="4" t="n">
+        <v>46193</v>
       </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
@@ -7332,16 +7245,14 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000457689 | PEDIDO(S) ASSOCIADO(S): [0030005383]</t>
+          <t>REFERENTE A NF 000457689</t>
         </is>
       </c>
       <c r="X53" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>05/07/26</t>
-        </is>
+      <c r="Y53" s="4" t="n">
+        <v>46208</v>
       </c>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
@@ -7461,16 +7372,14 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000457689 | PEDIDO(S) ASSOCIADO(S): [0030005383]</t>
+          <t>REFERENTE A NF 000457689</t>
         </is>
       </c>
       <c r="X54" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>20/07/26</t>
-        </is>
+      <c r="Y54" s="4" t="n">
+        <v>46223</v>
       </c>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
@@ -7590,16 +7499,14 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000046008 | PEDIDO(S) ASSOCIADO(S): [0030005316] CRISTINA - REF A MENSALIDADE DO SISTEMA NF 46008 BOLETO - NOTA COM RETENÇÃO DE IMPOSTO IRRF R$ 29,39 CSLL R$ 19,59 COFINS R$ 58,77 PIS R$ 12,73 VALOR A PAGAR R$ 1.838,52</t>
+          <t>REFERENTE A NF 000046008</t>
         </is>
       </c>
       <c r="X55" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y55" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z55" s="3" t="n">
         <v>46157</v>
@@ -7721,16 +7628,14 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000046151 | PEDIDO(S) ASSOCIADO(S): [0030005368] CRISTINA - REF A SUPORTE EXTRA DO SISTEMA A CARGA DE INVENTÁRIO REALIZADO PELO VAGNER (CONSULTOR). NF 46151 BOLETO - NOTA COM RETENÇÃO DE IMPOSTO CONTRIBUIÇÕES SOCIAIS: $4,05 COFINS R$12,15 PIS R$ 2,63 VALOR A PAGAR R$ 386,17</t>
+          <t>REFERENTE A NF 000046151</t>
         </is>
       </c>
       <c r="X56" s="3" t="n">
         <v>46162</v>
       </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y56" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z56" s="3" t="n">
         <v>46167</v>
@@ -7852,18 +7757,18 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000084433 | PEDIDO(S) ASSOCIADO(S): [0030005374] Cristina - referente a compra de material para uso interno, Brocas para furar postinho NF: 84433 Boleto 15/06</t>
+          <t>REFERENTE A NF 000084433</t>
         </is>
       </c>
       <c r="X57" s="3" t="n">
         <v>46162</v>
       </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>15/06/26</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr"/>
+      <c r="Y57" s="4" t="n">
+        <v>46188</v>
+      </c>
+      <c r="Z57" s="3" t="n">
+        <v>46188</v>
+      </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
@@ -7981,16 +7886,14 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001182205 | PEDIDO(S) ASSOCIADO(S): [0030005283]</t>
+          <t>REFERENTE A NF 001182205</t>
         </is>
       </c>
       <c r="X58" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>22/05/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y58" s="4" t="n">
+        <v>46164</v>
       </c>
       <c r="Z58" s="3" t="n">
         <v>46164</v>
@@ -8112,19 +8015,17 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001182205 | PEDIDO(S) ASSOCIADO(S): [0030005283]</t>
+          <t>REFERENTE A NF 001182205</t>
         </is>
       </c>
       <c r="X59" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>08/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y59" s="4" t="n">
+        <v>46181</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr">
@@ -8243,16 +8144,14 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001182205 | PEDIDO(S) ASSOCIADO(S): [0030005283]</t>
+          <t>REFERENTE A NF 001182205</t>
         </is>
       </c>
       <c r="X60" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>22/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y60" s="4" t="n">
+        <v>46195</v>
       </c>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr"/>
@@ -8372,19 +8271,17 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001187077 | PEDIDO(S) ASSOCIADO(S): [0030005313]</t>
+          <t>REFERENTE A NF 001187077</t>
         </is>
       </c>
       <c r="X61" s="3" t="n">
-        <v>46270</v>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>08/06/26</t>
-        </is>
+        <v>46151</v>
+      </c>
+      <c r="Y61" s="4" t="n">
+        <v>46181</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr">
@@ -8503,16 +8400,14 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001187077 | PEDIDO(S) ASSOCIADO(S): [0030005313]</t>
+          <t>REFERENTE A NF 001187077</t>
         </is>
       </c>
       <c r="X62" s="3" t="n">
-        <v>46270</v>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>23/06/26</t>
-        </is>
+        <v>46151</v>
+      </c>
+      <c r="Y62" s="4" t="n">
+        <v>46196</v>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
@@ -8632,16 +8527,14 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001187077 | PEDIDO(S) ASSOCIADO(S): [0030005313]</t>
+          <t>REFERENTE A NF 001187077</t>
         </is>
       </c>
       <c r="X63" s="3" t="n">
-        <v>46270</v>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>08/07/26</t>
-        </is>
+        <v>46151</v>
+      </c>
+      <c r="Y63" s="4" t="n">
+        <v>46211</v>
       </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
@@ -8761,16 +8654,14 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001660825 | PEDIDO(S) ASSOCIADO(S): [0030005393]</t>
+          <t>REFERENTE A NF 001660825</t>
         </is>
       </c>
       <c r="X64" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y64" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
@@ -8890,16 +8781,14 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001660825 | PEDIDO(S) ASSOCIADO(S): [0030005393]</t>
+          <t>REFERENTE A NF 001660825</t>
         </is>
       </c>
       <c r="X65" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>10/07/26</t>
-        </is>
+      <c r="Y65" s="4" t="n">
+        <v>46213</v>
       </c>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
@@ -9019,16 +8908,14 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001660825 | PEDIDO(S) ASSOCIADO(S): [0030005393]</t>
+          <t>REFERENTE A NF 001660825</t>
         </is>
       </c>
       <c r="X66" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>27/07/26</t>
-        </is>
+      <c r="Y66" s="4" t="n">
+        <v>46230</v>
       </c>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
@@ -9148,18 +9035,18 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="X67" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>11/06/26</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr"/>
+        <v>46154</v>
+      </c>
+      <c r="Y67" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>46184</v>
+      </c>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
@@ -9277,16 +9164,14 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="X68" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>22/06/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y68" s="4" t="n">
+        <v>46195</v>
       </c>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
@@ -9406,16 +9291,14 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="X69" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>01/07/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y69" s="4" t="n">
+        <v>46204</v>
       </c>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
@@ -9535,16 +9418,14 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371420 | PEDIDO(S) ASSOCIADO(S): [0030005365]</t>
+          <t>REFERENTE A NF 000371420</t>
         </is>
       </c>
       <c r="X70" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>13/07/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y70" s="4" t="n">
+        <v>46216</v>
       </c>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
@@ -9664,16 +9545,14 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="X71" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>17/06/26</t>
-        </is>
+      <c r="Y71" s="4" t="n">
+        <v>46190</v>
       </c>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
@@ -9793,16 +9672,14 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="X72" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>17/07/26</t>
-        </is>
+      <c r="Y72" s="4" t="n">
+        <v>46220</v>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
@@ -9922,16 +9799,14 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="X73" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>16/08/26</t>
-        </is>
+      <c r="Y73" s="4" t="n">
+        <v>46250</v>
       </c>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
@@ -10051,16 +9926,14 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000371769 | PEDIDO(S) ASSOCIADO(S): [0030005204]</t>
+          <t>REFERENTE A NF 000371769</t>
         </is>
       </c>
       <c r="X74" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>15/09/26</t>
-        </is>
+      <c r="Y74" s="4" t="n">
+        <v>46280</v>
       </c>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
@@ -10178,19 +10051,17 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000401 | PEDIDO(S) ASSOCIADO(S): [0030005353] Cristina - referente ao envio de amostras de um material que pretendemos trabalhar, quem está representando é o Cristiano ( inventário). Autorizado pelo Renato. NF 01 BOLETO 05/06</t>
+          <t>REFERENTE A NF 000000401</t>
         </is>
       </c>
       <c r="X75" s="3" t="n">
+        <v>46148</v>
+      </c>
+      <c r="Y75" s="4" t="n">
         <v>46178</v>
       </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>05/06/26</t>
-        </is>
-      </c>
       <c r="Z75" s="3" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr">
@@ -10307,19 +10178,17 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000403878 | PEDIDO(S) ASSOCIADO(S): [0030005387]</t>
+          <t>REFERENTE A NF 000403878</t>
         </is>
       </c>
       <c r="X76" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>03/06/26</t>
-        </is>
+      <c r="Y76" s="4" t="n">
+        <v>46176</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>46087</v>
+        <v>46176</v>
       </c>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr">
@@ -10438,16 +10307,14 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000451912 | [GIULIANA] REF A MENSALIDADE ACIPP-COMPETENCIA 04/2026 -VENCIMENTO 15/05/2026-PAGAMENTO VIA BOLETO BANCARIO</t>
+          <t>REFERENTE A NF 000451912</t>
         </is>
       </c>
       <c r="X77" s="3" t="n">
         <v>46156</v>
       </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y77" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z77" s="3" t="n">
         <v>46157</v>
@@ -10569,18 +10436,18 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000791405 | PEDIDO(S) ASSOCIADO(S): [0030005384]</t>
+          <t>REFERENTE A NF 000791405</t>
         </is>
       </c>
       <c r="X78" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>11/06/26</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Y78" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>46184</v>
+      </c>
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr">
         <is>
@@ -10698,16 +10565,14 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000791405 | PEDIDO(S) ASSOCIADO(S): [0030005384]</t>
+          <t>REFERENTE A NF 000791405</t>
         </is>
       </c>
       <c r="X79" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>18/06/26</t>
-        </is>
+      <c r="Y79" s="4" t="n">
+        <v>46191</v>
       </c>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
@@ -10827,16 +10692,14 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000791405 | PEDIDO(S) ASSOCIADO(S): [0030005384]</t>
+          <t>REFERENTE A NF 000791405</t>
         </is>
       </c>
       <c r="X80" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y80" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
@@ -10956,18 +10819,18 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165307 | PEDIDO(S) ASSOCIADO(S): [0030005362]</t>
+          <t>REFERENTE A NF 000165307</t>
         </is>
       </c>
       <c r="X81" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>14/06/26</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr"/>
+      <c r="Y81" s="4" t="n">
+        <v>46187</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>46188</v>
+      </c>
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr">
         <is>
@@ -11085,16 +10948,14 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165307 | PEDIDO(S) ASSOCIADO(S): [0030005362]</t>
+          <t>REFERENTE A NF 000165307</t>
         </is>
       </c>
       <c r="X82" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>29/06/26</t>
-        </is>
+      <c r="Y82" s="4" t="n">
+        <v>46202</v>
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
@@ -11214,16 +11075,14 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165307 | PEDIDO(S) ASSOCIADO(S): [0030005362]</t>
+          <t>REFERENTE A NF 000165307</t>
         </is>
       </c>
       <c r="X83" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>14/07/26</t>
-        </is>
+      <c r="Y83" s="4" t="n">
+        <v>46217</v>
       </c>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
@@ -11343,18 +11202,18 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000057700 | PEDIDO(S) ASSOCIADO(S): [0030005231]</t>
+          <t>REFERENTE A NF 000057700</t>
         </is>
       </c>
       <c r="X84" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>14/06/26</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr"/>
+      <c r="Y84" s="4" t="n">
+        <v>46187</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>46188</v>
+      </c>
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr">
         <is>
@@ -11472,16 +11331,14 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000057700 | PEDIDO(S) ASSOCIADO(S): [0030005231]</t>
+          <t>REFERENTE A NF 000057700</t>
         </is>
       </c>
       <c r="X85" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>29/06/26</t>
-        </is>
+      <c r="Y85" s="4" t="n">
+        <v>46202</v>
       </c>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
@@ -11601,16 +11458,14 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000057700 | PEDIDO(S) ASSOCIADO(S): [0030005231]</t>
+          <t>REFERENTE A NF 000057700</t>
         </is>
       </c>
       <c r="X86" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>14/07/26</t>
-        </is>
+      <c r="Y86" s="4" t="n">
+        <v>46217</v>
       </c>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr"/>
@@ -11730,16 +11585,14 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098776 | PEDIDO(S) ASSOCIADO(S): [0030005221]</t>
+          <t>REFERENTE A NF 000098776</t>
         </is>
       </c>
       <c r="X87" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>21/06/26</t>
-        </is>
+      <c r="Y87" s="4" t="n">
+        <v>46194</v>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
@@ -11859,16 +11712,14 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098776 | PEDIDO(S) ASSOCIADO(S): [0030005221]</t>
+          <t>REFERENTE A NF 000098776</t>
         </is>
       </c>
       <c r="X88" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>06/07/26</t>
-        </is>
+      <c r="Y88" s="4" t="n">
+        <v>46209</v>
       </c>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
@@ -11988,16 +11839,14 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098776 | PEDIDO(S) ASSOCIADO(S): [0030005221]</t>
+          <t>REFERENTE A NF 000098776</t>
         </is>
       </c>
       <c r="X89" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>21/07/26</t>
-        </is>
+      <c r="Y89" s="4" t="n">
+        <v>46224</v>
       </c>
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr"/>
@@ -12117,16 +11966,14 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098777 | PEDIDO(S) ASSOCIADO(S): [0030005363]</t>
+          <t>REFERENTE A NF 000098777</t>
         </is>
       </c>
       <c r="X90" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>21/06/26</t>
-        </is>
+      <c r="Y90" s="4" t="n">
+        <v>46194</v>
       </c>
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="inlineStr"/>
@@ -12246,16 +12093,14 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098777 | PEDIDO(S) ASSOCIADO(S): [0030005363]</t>
+          <t>REFERENTE A NF 000098777</t>
         </is>
       </c>
       <c r="X91" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>06/07/26</t>
-        </is>
+      <c r="Y91" s="4" t="n">
+        <v>46209</v>
       </c>
       <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="inlineStr"/>
@@ -12375,16 +12220,14 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000098777 | PEDIDO(S) ASSOCIADO(S): [0030005363]</t>
+          <t>REFERENTE A NF 000098777</t>
         </is>
       </c>
       <c r="X92" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>21/07/26</t>
-        </is>
+      <c r="Y92" s="4" t="n">
+        <v>46224</v>
       </c>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr"/>
@@ -12504,16 +12347,14 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 027590003 | PEDIDO(S) ASSOCIADO(S): [0030005377] CRISTINA - REF A RECARGA DO GOOGLE VENC. 24/05 boleto</t>
+          <t>REFERENTE A NF 027590003</t>
         </is>
       </c>
       <c r="X93" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>24/05/26</t>
-        </is>
+      <c r="Y93" s="4" t="n">
+        <v>46166</v>
       </c>
       <c r="Z93" s="3" t="n">
         <v>46167</v>
@@ -12635,19 +12476,17 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000071810 | PEDIDO(S) ASSOCIADO(S): [0030005334] CRISTINA - REF A COMPRA DE CAFE NF 71810 BOLETO 05/06</t>
+          <t>REFERENTE A NF 000071810</t>
         </is>
       </c>
       <c r="X94" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>05/06/26</t>
-        </is>
+      <c r="Y94" s="4" t="n">
+        <v>46178</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr">
@@ -12766,16 +12605,14 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000013466 | PEDIDO(S) ASSOCIADO(S): [0030005369]</t>
+          <t>REFERENTE A NF 000013466</t>
         </is>
       </c>
       <c r="X95" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>17/06/26</t>
-        </is>
+      <c r="Y95" s="4" t="n">
+        <v>46190</v>
       </c>
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr"/>
@@ -12895,16 +12732,14 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000013466 | PEDIDO(S) ASSOCIADO(S): [0030005369]</t>
+          <t>REFERENTE A NF 000013466</t>
         </is>
       </c>
       <c r="X96" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>02/07/26</t>
-        </is>
+      <c r="Y96" s="4" t="n">
+        <v>46205</v>
       </c>
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr"/>
@@ -13024,16 +12859,14 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000013466 | PEDIDO(S) ASSOCIADO(S): [0030005369]</t>
+          <t>REFERENTE A NF 000013466</t>
         </is>
       </c>
       <c r="X97" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>17/07/26</t>
-        </is>
+      <c r="Y97" s="4" t="n">
+        <v>46220</v>
       </c>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr"/>
@@ -13153,16 +12986,14 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014113 | PEDIDO(S) ASSOCIADO(S): [0030005378]</t>
+          <t>REFERENTE A NF 000014113</t>
         </is>
       </c>
       <c r="X98" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>19/06/26</t>
-        </is>
+      <c r="Y98" s="4" t="n">
+        <v>46192</v>
       </c>
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr"/>
@@ -13282,16 +13113,14 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014113 | PEDIDO(S) ASSOCIADO(S): [0030005378]</t>
+          <t>REFERENTE A NF 000014113</t>
         </is>
       </c>
       <c r="X99" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>03/07/26</t>
-        </is>
+      <c r="Y99" s="4" t="n">
+        <v>46206</v>
       </c>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr"/>
@@ -13411,16 +13240,14 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014113 | PEDIDO(S) ASSOCIADO(S): [0030005378]</t>
+          <t>REFERENTE A NF 000014113</t>
         </is>
       </c>
       <c r="X100" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>17/07/26</t>
-        </is>
+      <c r="Y100" s="4" t="n">
+        <v>46220</v>
       </c>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr"/>
@@ -13540,16 +13367,14 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014125 | PEDIDO(S) ASSOCIADO(S): [0030005364]</t>
+          <t>REFERENTE A NF 000014125</t>
         </is>
       </c>
       <c r="X101" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>19/06/26</t>
-        </is>
+      <c r="Y101" s="4" t="n">
+        <v>46192</v>
       </c>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr"/>
@@ -13669,16 +13494,14 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014125 | PEDIDO(S) ASSOCIADO(S): [0030005364]</t>
+          <t>REFERENTE A NF 000014125</t>
         </is>
       </c>
       <c r="X102" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>03/07/26</t>
-        </is>
+      <c r="Y102" s="4" t="n">
+        <v>46206</v>
       </c>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr"/>
@@ -13798,16 +13621,14 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014125 | PEDIDO(S) ASSOCIADO(S): [0030005364]</t>
+          <t>REFERENTE A NF 000014125</t>
         </is>
       </c>
       <c r="X103" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>20/07/26</t>
-        </is>
+      <c r="Y103" s="4" t="n">
+        <v>46223</v>
       </c>
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr"/>
@@ -13927,16 +13748,14 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014126 | PEDIDO(S) ASSOCIADO(S): [0030005376]</t>
+          <t>REFERENTE A NF 000014126</t>
         </is>
       </c>
       <c r="X104" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>19/06/26</t>
-        </is>
+      <c r="Y104" s="4" t="n">
+        <v>46192</v>
       </c>
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr"/>
@@ -14056,16 +13875,14 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014126 | PEDIDO(S) ASSOCIADO(S): [0030005376]</t>
+          <t>REFERENTE A NF 000014126</t>
         </is>
       </c>
       <c r="X105" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>03/07/26</t>
-        </is>
+      <c r="Y105" s="4" t="n">
+        <v>46206</v>
       </c>
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr"/>
@@ -14185,16 +14002,14 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014126 | PEDIDO(S) ASSOCIADO(S): [0030005376]</t>
+          <t>REFERENTE A NF 000014126</t>
         </is>
       </c>
       <c r="X106" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>20/07/26</t>
-        </is>
+      <c r="Y106" s="4" t="n">
+        <v>46223</v>
       </c>
       <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="inlineStr"/>
@@ -14314,16 +14129,14 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014139 | PEDIDO(S) ASSOCIADO(S): [0030005392]</t>
+          <t>REFERENTE A NF 000014139</t>
         </is>
       </c>
       <c r="X107" s="3" t="n">
         <v>46166</v>
       </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>23/06/26</t>
-        </is>
+      <c r="Y107" s="4" t="n">
+        <v>46196</v>
       </c>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr"/>
@@ -14443,16 +14256,14 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014139 | PEDIDO(S) ASSOCIADO(S): [0030005392]</t>
+          <t>REFERENTE A NF 000014139</t>
         </is>
       </c>
       <c r="X108" s="3" t="n">
         <v>46166</v>
       </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>07/07/26</t>
-        </is>
+      <c r="Y108" s="4" t="n">
+        <v>46210</v>
       </c>
       <c r="Z108" t="inlineStr"/>
       <c r="AA108" t="inlineStr"/>
@@ -14572,16 +14383,14 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000014139 | PEDIDO(S) ASSOCIADO(S): [0030005392]</t>
+          <t>REFERENTE A NF 000014139</t>
         </is>
       </c>
       <c r="X109" s="3" t="n">
         <v>46166</v>
       </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>22/07/26</t>
-        </is>
+      <c r="Y109" s="4" t="n">
+        <v>46225</v>
       </c>
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr"/>
@@ -14701,16 +14510,14 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000016346 | PEDIDO(S) ASSOCIADO(S): [0030005375] Cristina - Referente a compra de cintas para uso no patio NF: 16346 Boleto 17/06</t>
+          <t>REFERENTE A NF 000016346</t>
         </is>
       </c>
       <c r="X110" s="3" t="n">
         <v>46162</v>
       </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>17/06/26</t>
-        </is>
+      <c r="Y110" s="4" t="n">
+        <v>46190</v>
       </c>
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr"/>
@@ -14830,16 +14637,14 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000165537 | PEDIDO(S) ASSOCIADO(S): [0030005347] Cristina - Referente a compra de materiais de escritório para reabastecimento de estoque. NF 165537 BOLETO 25/05</t>
+          <t>REFERENTE A NF 000165537</t>
         </is>
       </c>
       <c r="X111" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y111" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z111" s="3" t="n">
         <v>46167</v>
@@ -14961,16 +14766,14 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029231 | PEDIDO(S) ASSOCIADO(S): [0030005344]</t>
+          <t>REFERENTE A NF 000029231</t>
         </is>
       </c>
       <c r="X112" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>22/06/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y112" s="4" t="n">
+        <v>46195</v>
       </c>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr"/>
@@ -15090,16 +14893,14 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029231 | PEDIDO(S) ASSOCIADO(S): [0030005344]</t>
+          <t>REFERENTE A NF 000029231</t>
         </is>
       </c>
       <c r="X113" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>06/07/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y113" s="4" t="n">
+        <v>46209</v>
       </c>
       <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr"/>
@@ -15219,16 +15020,14 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000029231 | PEDIDO(S) ASSOCIADO(S): [0030005344]</t>
+          <t>REFERENTE A NF 000029231</t>
         </is>
       </c>
       <c r="X114" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>20/07/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y114" s="4" t="n">
+        <v>46223</v>
       </c>
       <c r="Z114" t="inlineStr"/>
       <c r="AA114" t="inlineStr"/>
@@ -15348,16 +15147,14 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="X115" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y115" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z115" s="3" t="n">
         <v>46168</v>
@@ -15479,19 +15276,17 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="X116" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>05/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y116" s="4" t="n">
+        <v>46178</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="AA116" t="inlineStr"/>
       <c r="AB116" t="inlineStr">
@@ -15610,16 +15405,14 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="X117" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>15/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y117" s="4" t="n">
+        <v>46188</v>
       </c>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr"/>
@@ -15739,16 +15532,14 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="X118" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y118" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z118" t="inlineStr"/>
       <c r="AA118" t="inlineStr"/>
@@ -15868,16 +15659,14 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320095 | PEDIDO(S) ASSOCIADO(S): [0030005071]</t>
+          <t>REFERENTE A NF 000320095</t>
         </is>
       </c>
       <c r="X119" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>05/07/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y119" s="4" t="n">
+        <v>46208</v>
       </c>
       <c r="Z119" t="inlineStr"/>
       <c r="AA119" t="inlineStr"/>
@@ -15997,16 +15786,14 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="X120" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y120" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z120" s="3" t="n">
         <v>46168</v>
@@ -16128,19 +15915,17 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="X121" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>05/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y121" s="4" t="n">
+        <v>46178</v>
       </c>
       <c r="Z121" s="3" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr">
@@ -16259,16 +16044,14 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="X122" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>15/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y122" s="4" t="n">
+        <v>46188</v>
       </c>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
@@ -16388,16 +16171,14 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="X123" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y123" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="inlineStr"/>
@@ -16517,16 +16298,14 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000320096 | PEDIDO(S) ASSOCIADO(S): [0030005107]</t>
+          <t>REFERENTE A NF 000320096</t>
         </is>
       </c>
       <c r="X124" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>06/07/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y124" s="4" t="n">
+        <v>46209</v>
       </c>
       <c r="Z124" t="inlineStr"/>
       <c r="AA124" t="inlineStr"/>
@@ -16646,19 +16425,17 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000333 | PEDIDO(S) ASSOCIADO(S): [0030005340] CRISTINA - REFERENTE A COMPRA DE MATERIAS EPÍS PARA REABASTECIMENTO DO ESTOQUE DE USO DOS COLABORADORES. NF 333 BOLETO 02/06</t>
+          <t>REFERENTE A NF 000000333</t>
         </is>
       </c>
       <c r="X125" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>02/06/26</t>
-        </is>
+      <c r="Y125" s="4" t="n">
+        <v>46175</v>
       </c>
       <c r="Z125" s="3" t="n">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="AA125" t="inlineStr"/>
       <c r="AB125" t="inlineStr">
@@ -16775,18 +16552,18 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000448575 | PEDIDO(S) ASSOCIADO(S): [0030005359] Cristina - Referente a compra de tomada para instalação da roletadeira no pátio. NF 448575 - BOLETO 13/06</t>
+          <t>REFERENTE A NF 000448575</t>
         </is>
       </c>
       <c r="X126" s="3" t="n">
         <v>46156</v>
       </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>13/06/26</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr"/>
+      <c r="Y126" s="4" t="n">
+        <v>46186</v>
+      </c>
+      <c r="Z126" s="3" t="n">
+        <v>46188</v>
+      </c>
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr">
         <is>
@@ -16904,19 +16681,17 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000468 | PEDIDO(S) ASSOCIADO(S): [0030005360] Cristina - Compra referente a reposição de tintas para organização de materiais do estoque. NF 468 BOLETO 2X</t>
+          <t>REFERENTE A NF 000000468</t>
         </is>
       </c>
       <c r="X127" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>05/06/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y127" s="4" t="n">
+        <v>46178</v>
       </c>
       <c r="Z127" s="3" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
@@ -17035,18 +16810,18 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000468 | PEDIDO(S) ASSOCIADO(S): [0030005360] Cristina - Compra referente a reposição de tintas para organização de materiais do estoque. NF 468 BOLETO 2X</t>
+          <t>REFERENTE A NF 000000468</t>
         </is>
       </c>
       <c r="X128" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>15/06/26</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr"/>
+        <v>46154</v>
+      </c>
+      <c r="Y128" s="4" t="n">
+        <v>46188</v>
+      </c>
+      <c r="Z128" s="3" t="n">
+        <v>46188</v>
+      </c>
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr">
         <is>
@@ -17162,18 +16937,18 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000005627 | PEDIDO(S) ASSOCIADO(S): [0030005357] Cristina - Referente a compra de uniformes para uso de colaboradores. NF 5627 Boleto 2x</t>
+          <t>REFERENTE A NF 000005627</t>
         </is>
       </c>
       <c r="X129" s="3" t="n">
         <v>46155</v>
       </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>12/06/26</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr"/>
+      <c r="Y129" s="4" t="n">
+        <v>46185</v>
+      </c>
+      <c r="Z129" s="3" t="n">
+        <v>46185</v>
+      </c>
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr">
         <is>
@@ -17289,16 +17064,14 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000005627 | PEDIDO(S) ASSOCIADO(S): [0030005357] Cristina - Referente a compra de uniformes para uso de colaboradores. NF 5627 Boleto 2x</t>
+          <t>REFERENTE A NF 000005627</t>
         </is>
       </c>
       <c r="X130" s="3" t="n">
         <v>46155</v>
       </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>12/07/26</t>
-        </is>
+      <c r="Y130" s="4" t="n">
+        <v>46215</v>
       </c>
       <c r="Z130" t="inlineStr"/>
       <c r="AA130" t="inlineStr"/>
@@ -17418,19 +17191,17 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000006598 | PEDIDO(S) ASSOCIADO(S): [0030005329] Cristina - Referente a compra de refeição para café da manhã do pessoal presente para a contagem no dia 01/05 (sexta) NF6598 BOLETO 11/05</t>
+          <t>REFERENTE A NF 000006598</t>
         </is>
       </c>
       <c r="X131" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y131" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z131" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr">
@@ -17549,19 +17320,17 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000006599 | PEDIDO(S) ASSOCIADO(S): [0030005330] Cristina - Referente a compra de refeição para café da manhã do pessoal presente para a contagem no dia 02/05 (sábado) NF6599 BOLETO 11/05</t>
+          <t>REFERENTE A NF 000006599</t>
         </is>
       </c>
       <c r="X132" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y132" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
@@ -17680,19 +17449,17 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000006628 | PEDIDO(S) ASSOCIADO(S): [0030005331] Cristina - Referente a compra de refeição para café da manhã do pessoal presente para a contagem no dia 03/05 (domingo) NF6628 BOLETO 12/05</t>
+          <t>REFERENTE A NF 000006628</t>
         </is>
       </c>
       <c r="X133" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>12/05/26</t>
-        </is>
+      <c r="Y133" s="4" t="n">
+        <v>46154</v>
       </c>
       <c r="Z133" s="3" t="n">
-        <v>46361</v>
+        <v>46154</v>
       </c>
       <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr">
@@ -17811,16 +17578,14 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001013752 | PEDIDO(S) ASSOCIADO(S): [0030005358]</t>
+          <t>REFERENTE A NF 001013752</t>
         </is>
       </c>
       <c r="X134" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y134" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z134" s="3" t="n">
         <v>46168</v>
@@ -17942,19 +17707,17 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001013752 | PEDIDO(S) ASSOCIADO(S): [0030005358]</t>
+          <t>REFERENTE A NF 001013752</t>
         </is>
       </c>
       <c r="X135" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>02/06/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y135" s="4" t="n">
+        <v>46175</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="inlineStr">
@@ -18073,19 +17836,17 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001013752 | PEDIDO(S) ASSOCIADO(S): [0030005358]</t>
+          <t>REFERENTE A NF 001013752</t>
         </is>
       </c>
       <c r="X136" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>09/06/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y136" s="4" t="n">
+        <v>46182</v>
       </c>
       <c r="Z136" s="3" t="n">
-        <v>46271</v>
+        <v>46182</v>
       </c>
       <c r="AA136" t="inlineStr"/>
       <c r="AB136" t="inlineStr">
@@ -18204,19 +17965,17 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000405509 | PEDIDO(S) ASSOCIADO(S): [0030005373]</t>
+          <t>REFERENTE A NF 000405509</t>
         </is>
       </c>
       <c r="X137" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>02/06/26</t>
-        </is>
+      <c r="Y137" s="4" t="n">
+        <v>46175</v>
       </c>
       <c r="Z137" s="3" t="n">
-        <v>46059</v>
+        <v>46175</v>
       </c>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
@@ -18335,19 +18094,17 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000405509 | PEDIDO(S) ASSOCIADO(S): [0030005373]</t>
+          <t>REFERENTE A NF 000405509</t>
         </is>
       </c>
       <c r="X138" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>09/06/26</t>
-        </is>
+      <c r="Y138" s="4" t="n">
+        <v>46182</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>46271</v>
+        <v>46182</v>
       </c>
       <c r="AA138" t="inlineStr"/>
       <c r="AB138" t="inlineStr">
@@ -18466,18 +18223,18 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000405509 | PEDIDO(S) ASSOCIADO(S): [0030005373]</t>
+          <t>REFERENTE A NF 000405509</t>
         </is>
       </c>
       <c r="X139" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>16/06/26</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr"/>
+      <c r="Y139" s="4" t="n">
+        <v>46189</v>
+      </c>
+      <c r="Z139" s="3" t="n">
+        <v>46189</v>
+      </c>
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr">
         <is>
@@ -18595,19 +18352,17 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001014842 | PEDIDO(S) ASSOCIADO(S): [0030005380]</t>
+          <t>REFERENTE A NF 001014842</t>
         </is>
       </c>
       <c r="X140" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>04/06/26</t>
-        </is>
+      <c r="Y140" s="4" t="n">
+        <v>46177</v>
       </c>
       <c r="Z140" s="3" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr">
@@ -18726,18 +18481,18 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001014842 | PEDIDO(S) ASSOCIADO(S): [0030005380]</t>
+          <t>REFERENTE A NF 001014842</t>
         </is>
       </c>
       <c r="X141" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>11/06/26</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr"/>
+      <c r="Y141" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="Z141" s="3" t="n">
+        <v>46184</v>
+      </c>
       <c r="AA141" t="inlineStr"/>
       <c r="AB141" t="inlineStr">
         <is>
@@ -18855,16 +18610,14 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 001014842 | PEDIDO(S) ASSOCIADO(S): [0030005380]</t>
+          <t>REFERENTE A NF 001014842</t>
         </is>
       </c>
       <c r="X142" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>18/06/26</t>
-        </is>
+      <c r="Y142" s="4" t="n">
+        <v>46191</v>
       </c>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
@@ -18984,16 +18737,14 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>REF AJUDA DE CUSTO COMP MAIO 2026 | PAGTO REF AJUDA DE CUSTO ESTAGIARIA COMP MAIO 2026. AMANDA SANTOS SALOMÃO / BANCO: NUBANK / AG: 0001 / C/C 92051644-5 / CHAVE PIX: CPF 394.052.338-07</t>
+          <t>REF AJUDA DE CUSTO COMP MAIO 2026</t>
         </is>
       </c>
       <c r="X143" s="3" t="n">
         <v>46167</v>
       </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+      <c r="Y143" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z143" s="3" t="n">
         <v>46168</v>
@@ -19115,15 +18866,13 @@
       </c>
       <c r="W144" t="inlineStr"/>
       <c r="X144" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y144" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z144" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr">
@@ -19242,15 +18991,13 @@
       </c>
       <c r="W145" t="inlineStr"/>
       <c r="X145" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y145" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z145" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="inlineStr">
@@ -19369,15 +19116,13 @@
       </c>
       <c r="W146" t="inlineStr"/>
       <c r="X146" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y146" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z146" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr">
@@ -19498,10 +19243,8 @@
       <c r="X147" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>05/05/26</t>
-        </is>
+      <c r="Y147" s="4" t="n">
+        <v>46147</v>
       </c>
       <c r="Z147" s="3" t="n">
         <v>46147</v>
@@ -19625,10 +19368,8 @@
       <c r="X148" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>05/05/26</t>
-        </is>
+      <c r="Y148" s="4" t="n">
+        <v>46147</v>
       </c>
       <c r="Z148" s="3" t="n">
         <v>46147</v>
@@ -19750,16 +19491,14 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>referente a fatura ikatec | CRISTINA - REF A CONTRATAÇÃO DO SISTEMA DIGISAC VENCIMENTO 18/05 NOTA SERA EMITIDA APOS O PAGAMENTO</t>
+          <t>referente a fatura ikatec</t>
         </is>
       </c>
       <c r="X149" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y149" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z149" s="3" t="n">
         <v>46160</v>
@@ -19881,19 +19620,17 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA | ESTORNO DE CREDITO DE COMPRA DEVOLVIDA Conta: 40518-4, Ag: 0337, Banco: Caixa Econômica Federal, Chave pix: 18997649207, Nome: LUIS FERNANDO CANO RIBOLI R$ 960,00</t>
+          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA</t>
         </is>
       </c>
       <c r="X150" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y150" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z150" s="3" t="n">
-        <v>46208</v>
+        <v>46149</v>
       </c>
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr">
@@ -20012,15 +19749,13 @@
       </c>
       <c r="W151" t="inlineStr"/>
       <c r="X151" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>06/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y151" s="4" t="n">
+        <v>46148</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>46178</v>
+        <v>46148</v>
       </c>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr">
@@ -20139,15 +19874,13 @@
       </c>
       <c r="W152" t="inlineStr"/>
       <c r="X152" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>06/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y152" s="4" t="n">
+        <v>46148</v>
       </c>
       <c r="Z152" s="3" t="n">
-        <v>46178</v>
+        <v>46148</v>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr">
@@ -20266,15 +19999,13 @@
       </c>
       <c r="W153" t="inlineStr"/>
       <c r="X153" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>06/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y153" s="4" t="n">
+        <v>46148</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>46178</v>
+        <v>46148</v>
       </c>
       <c r="AA153" t="inlineStr"/>
       <c r="AB153" t="inlineStr">
@@ -20393,15 +20124,13 @@
       </c>
       <c r="W154" t="inlineStr"/>
       <c r="X154" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y154" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z154" s="3" t="n">
-        <v>46208</v>
+        <v>46149</v>
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr">
@@ -20520,15 +20249,13 @@
       </c>
       <c r="W155" t="inlineStr"/>
       <c r="X155" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y155" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>46208</v>
+        <v>46149</v>
       </c>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr">
@@ -20647,15 +20374,13 @@
       </c>
       <c r="W156" t="inlineStr"/>
       <c r="X156" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y156" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>46208</v>
+        <v>46149</v>
       </c>
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr">
@@ -20774,15 +20499,13 @@
       </c>
       <c r="W157" t="inlineStr"/>
       <c r="X157" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y157" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr">
@@ -20901,15 +20624,13 @@
       </c>
       <c r="W158" t="inlineStr"/>
       <c r="X158" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y158" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>46117</v>
+        <v>46146</v>
       </c>
       <c r="AA158" t="inlineStr"/>
       <c r="AB158" t="inlineStr">
@@ -21028,15 +20749,13 @@
       </c>
       <c r="W159" t="inlineStr"/>
       <c r="X159" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y159" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>46208</v>
+        <v>46149</v>
       </c>
       <c r="AA159" t="inlineStr"/>
       <c r="AB159" t="inlineStr">
@@ -21155,15 +20874,13 @@
       </c>
       <c r="W160" t="inlineStr"/>
       <c r="X160" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>08/05/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y160" s="4" t="n">
+        <v>46150</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>46239</v>
+        <v>46150</v>
       </c>
       <c r="AA160" t="inlineStr"/>
       <c r="AB160" t="inlineStr">
@@ -21282,15 +20999,13 @@
       </c>
       <c r="W161" t="inlineStr"/>
       <c r="X161" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y161" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z161" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA161" t="inlineStr"/>
       <c r="AB161" t="inlineStr">
@@ -21409,15 +21124,13 @@
       </c>
       <c r="W162" t="inlineStr"/>
       <c r="X162" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y162" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr">
@@ -21536,15 +21249,13 @@
       </c>
       <c r="W163" t="inlineStr"/>
       <c r="X163" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y163" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA163" t="inlineStr"/>
       <c r="AB163" t="inlineStr">
@@ -21663,15 +21374,13 @@
       </c>
       <c r="W164" t="inlineStr"/>
       <c r="X164" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y164" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z164" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA164" t="inlineStr"/>
       <c r="AB164" t="inlineStr">
@@ -21790,15 +21499,13 @@
       </c>
       <c r="W165" t="inlineStr"/>
       <c r="X165" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y165" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA165" t="inlineStr"/>
       <c r="AB165" t="inlineStr">
@@ -21917,15 +21624,13 @@
       </c>
       <c r="W166" t="inlineStr"/>
       <c r="X166" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y166" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z166" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA166" t="inlineStr"/>
       <c r="AB166" t="inlineStr">
@@ -22044,15 +21749,13 @@
       </c>
       <c r="W167" t="inlineStr"/>
       <c r="X167" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y167" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
@@ -22171,15 +21874,13 @@
       </c>
       <c r="W168" t="inlineStr"/>
       <c r="X168" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y168" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA168" t="inlineStr"/>
       <c r="AB168" t="inlineStr">
@@ -22298,15 +21999,13 @@
       </c>
       <c r="W169" t="inlineStr"/>
       <c r="X169" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>12/05/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y169" s="4" t="n">
+        <v>46154</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>46361</v>
+        <v>46154</v>
       </c>
       <c r="AA169" t="inlineStr"/>
       <c r="AB169" t="inlineStr">
@@ -22425,15 +22124,13 @@
       </c>
       <c r="W170" t="inlineStr"/>
       <c r="X170" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>12/05/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y170" s="4" t="n">
+        <v>46154</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>46361</v>
+        <v>46154</v>
       </c>
       <c r="AA170" t="inlineStr"/>
       <c r="AB170" t="inlineStr">
@@ -22554,10 +22251,8 @@
       <c r="X171" s="3" t="n">
         <v>46155</v>
       </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>13/05/26</t>
-        </is>
+      <c r="Y171" s="4" t="n">
+        <v>46155</v>
       </c>
       <c r="Z171" s="3" t="n">
         <v>46155</v>
@@ -22681,10 +22376,8 @@
       <c r="X172" s="3" t="n">
         <v>46155</v>
       </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>13/05/26</t>
-        </is>
+      <c r="Y172" s="4" t="n">
+        <v>46155</v>
       </c>
       <c r="Z172" s="3" t="n">
         <v>46155</v>
@@ -22808,10 +22501,8 @@
       <c r="X173" s="3" t="n">
         <v>46155</v>
       </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>13/05/26</t>
-        </is>
+      <c r="Y173" s="4" t="n">
+        <v>46155</v>
       </c>
       <c r="Z173" s="3" t="n">
         <v>46155</v>
@@ -22933,15 +22624,13 @@
       </c>
       <c r="W174" t="inlineStr"/>
       <c r="X174" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>08/05/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y174" s="4" t="n">
+        <v>46150</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>46239</v>
+        <v>46150</v>
       </c>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr">
@@ -23060,15 +22749,13 @@
       </c>
       <c r="W175" t="inlineStr"/>
       <c r="X175" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y175" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr">
@@ -23187,15 +22874,13 @@
       </c>
       <c r="W176" t="inlineStr"/>
       <c r="X176" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y176" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr">
@@ -23314,15 +22999,13 @@
       </c>
       <c r="W177" t="inlineStr"/>
       <c r="X177" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y177" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>46331</v>
+        <v>46153</v>
       </c>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr">
@@ -23441,16 +23124,14 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA | ESTORNO DE CREDITO DE COMPRA DEVOLVIDA Conta: 592540867-1, Ag: 2000, Banco: Caixa Econômica Federal, Chave pix: 18996055413, Nome: APARECIDO ALVES DE MOURA R$ 392,00</t>
+          <t>ESTORNO DE CREDITO DE COMPRA CANCELADA</t>
         </is>
       </c>
       <c r="X178" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+      <c r="Y178" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z178" s="3" t="n">
         <v>46160</v>
@@ -23572,16 +23253,14 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>referente a fatura 104187 | CRISTINA - REF A COMPRA DE ENERGIA INJETADA COMP. MÊS REFERÊNCIA 04/2026 - BOLETO BANCARIO VENCIMENTO 20/05- UC 9/2710610-3 e UC 9/4778547-2</t>
+          <t>referente a fatura 104187</t>
         </is>
       </c>
       <c r="X179" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>20/05/26</t>
-        </is>
+      <c r="Y179" s="4" t="n">
+        <v>46162</v>
       </c>
       <c r="Z179" s="3" t="n">
         <v>46162</v>
@@ -23703,16 +23382,14 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>REFERENTE A RECIBO | Cristina - Referente a quantia de R$ 1.200,00 (Hum mil e Duzentos reais) mais 5 convites no valor de R$ 400,00 (Quatrocentos Reais ) Referente patrocinio no XVI COSTELÃO DA AEAAPP para profissionais da aréa técnológica – AEAAPP, Associação dos Engenheiros, Arquitetos e Agrônomos de Presidente Prudente Solicitado por Renato/Zanuto Dados para pagamentos: Dados bancário para credito: Banco: Sicoob Paulista 456 Agência: 4446 - Conta: 13.369-8 ou Chave PIX/CNPJ: 44.860.666/0001-95 21/05</t>
+          <t>REFERENTE A RECIBO</t>
         </is>
       </c>
       <c r="X180" s="3" t="n">
         <v>46162</v>
       </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>21/05/26</t>
-        </is>
+      <c r="Y180" s="4" t="n">
+        <v>46163</v>
       </c>
       <c r="Z180" s="3" t="n">
         <v>46163</v>
@@ -23836,10 +23513,8 @@
       <c r="X181" s="3" t="n">
         <v>46156</v>
       </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>14/05/26</t>
-        </is>
+      <c r="Y181" s="4" t="n">
+        <v>46156</v>
       </c>
       <c r="Z181" s="3" t="n">
         <v>46156</v>
@@ -23963,10 +23638,8 @@
       <c r="X182" s="3" t="n">
         <v>46156</v>
       </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>14/05/26</t>
-        </is>
+      <c r="Y182" s="4" t="n">
+        <v>46156</v>
       </c>
       <c r="Z182" s="3" t="n">
         <v>46156</v>
@@ -24090,10 +23763,8 @@
       <c r="X183" s="3" t="n">
         <v>46156</v>
       </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>14/05/26</t>
-        </is>
+      <c r="Y183" s="4" t="n">
+        <v>46156</v>
       </c>
       <c r="Z183" s="3" t="n">
         <v>46156</v>
@@ -24217,10 +23888,8 @@
       <c r="X184" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y184" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z184" s="3" t="n">
         <v>46157</v>
@@ -24344,10 +24013,8 @@
       <c r="X185" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y185" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z185" s="3" t="n">
         <v>46157</v>
@@ -24471,10 +24138,8 @@
       <c r="X186" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+      <c r="Y186" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z186" s="3" t="n">
         <v>46157</v>
@@ -24598,10 +24263,8 @@
       <c r="X187" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+      <c r="Y187" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z187" s="3" t="n">
         <v>46160</v>
@@ -24725,10 +24388,8 @@
       <c r="X188" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+      <c r="Y188" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z188" s="3" t="n">
         <v>46160</v>
@@ -24852,10 +24513,8 @@
       <c r="X189" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+      <c r="Y189" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z189" s="3" t="n">
         <v>46160</v>
@@ -24979,10 +24638,8 @@
       <c r="X190" s="3" t="n">
         <v>46160</v>
       </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+      <c r="Y190" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z190" s="3" t="n">
         <v>46160</v>
@@ -25106,10 +24763,8 @@
       <c r="X191" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>19/05/26</t>
-        </is>
+      <c r="Y191" s="4" t="n">
+        <v>46161</v>
       </c>
       <c r="Z191" s="3" t="n">
         <v>46161</v>
@@ -25233,10 +24888,8 @@
       <c r="X192" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>19/05/26</t>
-        </is>
+      <c r="Y192" s="4" t="n">
+        <v>46161</v>
       </c>
       <c r="Z192" s="3" t="n">
         <v>46161</v>
@@ -25360,10 +25013,8 @@
       <c r="X193" s="3" t="n">
         <v>46162</v>
       </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>20/05/26</t>
-        </is>
+      <c r="Y193" s="4" t="n">
+        <v>46162</v>
       </c>
       <c r="Z193" s="3" t="n">
         <v>46162</v>
@@ -25487,10 +25138,8 @@
       <c r="X194" s="3" t="n">
         <v>46162</v>
       </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>20/05/26</t>
-        </is>
+      <c r="Y194" s="4" t="n">
+        <v>46162</v>
       </c>
       <c r="Z194" s="3" t="n">
         <v>46162</v>
@@ -25614,10 +25263,8 @@
       <c r="X195" s="3" t="n">
         <v>46162</v>
       </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>20/05/26</t>
-        </is>
+      <c r="Y195" s="4" t="n">
+        <v>46162</v>
       </c>
       <c r="Z195" s="3" t="n">
         <v>46162</v>
@@ -25741,10 +25388,8 @@
       <c r="X196" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>21/05/26</t>
-        </is>
+      <c r="Y196" s="4" t="n">
+        <v>46163</v>
       </c>
       <c r="Z196" s="3" t="n">
         <v>46163</v>
@@ -25868,10 +25513,8 @@
       <c r="X197" s="3" t="n">
         <v>46163</v>
       </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>21/05/26</t>
-        </is>
+      <c r="Y197" s="4" t="n">
+        <v>46163</v>
       </c>
       <c r="Z197" s="3" t="n">
         <v>46163</v>
@@ -25995,10 +25638,8 @@
       <c r="X198" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>22/05/26</t>
-        </is>
+      <c r="Y198" s="4" t="n">
+        <v>46164</v>
       </c>
       <c r="Z198" s="3" t="n">
         <v>46164</v>
@@ -26122,10 +25763,8 @@
       <c r="X199" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>22/05/26</t>
-        </is>
+      <c r="Y199" s="4" t="n">
+        <v>46164</v>
       </c>
       <c r="Z199" s="3" t="n">
         <v>46164</v>
@@ -26249,10 +25888,8 @@
       <c r="X200" s="3" t="n">
         <v>46164</v>
       </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>22/05/26</t>
-        </is>
+      <c r="Y200" s="4" t="n">
+        <v>46164</v>
       </c>
       <c r="Z200" s="3" t="n">
         <v>46164</v>
@@ -26376,10 +26013,8 @@
       <c r="X201" s="3" t="n">
         <v>46167</v>
       </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y201" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z201" s="3" t="n">
         <v>46167</v>
@@ -26503,10 +26138,8 @@
       <c r="X202" s="3" t="n">
         <v>46167</v>
       </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y202" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z202" s="3" t="n">
         <v>46167</v>
@@ -26630,10 +26263,8 @@
       <c r="X203" s="3" t="n">
         <v>46167</v>
       </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y203" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z203" s="3" t="n">
         <v>46167</v>
@@ -26757,10 +26388,8 @@
       <c r="X204" s="3" t="n">
         <v>46167</v>
       </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y204" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z204" s="3" t="n">
         <v>46167</v>
@@ -26884,10 +26513,8 @@
       <c r="X205" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+      <c r="Y205" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z205" s="3" t="n">
         <v>46168</v>
@@ -27011,10 +26638,8 @@
       <c r="X206" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+      <c r="Y206" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z206" s="3" t="n">
         <v>46168</v>
@@ -27138,10 +26763,8 @@
       <c r="X207" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>27/05/26</t>
-        </is>
+      <c r="Y207" s="4" t="n">
+        <v>46169</v>
       </c>
       <c r="Z207" s="3" t="n">
         <v>46169</v>
@@ -27265,10 +26888,8 @@
       <c r="X208" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>27/05/26</t>
-        </is>
+      <c r="Y208" s="4" t="n">
+        <v>46169</v>
       </c>
       <c r="Z208" s="3" t="n">
         <v>46169</v>
@@ -27392,10 +27013,8 @@
       <c r="X209" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>28/05/26</t>
-        </is>
+      <c r="Y209" s="4" t="n">
+        <v>46170</v>
       </c>
       <c r="Z209" s="3" t="n">
         <v>46170</v>
@@ -27519,10 +27138,8 @@
       <c r="X210" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>28/05/26</t>
-        </is>
+      <c r="Y210" s="4" t="n">
+        <v>46170</v>
       </c>
       <c r="Z210" s="3" t="n">
         <v>46170</v>
@@ -27646,10 +27263,8 @@
       <c r="X211" s="3" t="n">
         <v>46171</v>
       </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+      <c r="Y211" s="4" t="n">
+        <v>46171</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>46171</v>
@@ -27773,10 +27388,8 @@
       <c r="X212" s="3" t="n">
         <v>46171</v>
       </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+      <c r="Y212" s="4" t="n">
+        <v>46171</v>
       </c>
       <c r="Z212" s="3" t="n">
         <v>46171</v>
@@ -27898,16 +27511,14 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>PAGAMENTO EM DUPLICIDADE | PAGAMENTO REALIZADO EM DUPLICIDADE EM 25/05, O VALOR NÃO SERÁ DEVOLVIDO EM CONTA, SERÁ TROCADO EM MERCADORIA NO PRÓXIMO PEDIDO (AINDA SEM DATA PREVISTA), ZANUTO E LUCAS CIENTE</t>
+          <t>PAGAMENTO EM DUPLICIDADE</t>
         </is>
       </c>
       <c r="X213" s="3" t="n">
         <v>46167</v>
       </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+      <c r="Y213" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z213" s="3" t="n">
         <v>46167</v>
@@ -28031,10 +27642,8 @@
       <c r="X214" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>27/05/26</t>
-        </is>
+      <c r="Y214" s="4" t="n">
+        <v>46169</v>
       </c>
       <c r="Z214" s="3" t="n">
         <v>46169</v>
@@ -28158,10 +27767,8 @@
       <c r="X215" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>28/05/26</t>
-        </is>
+      <c r="Y215" s="4" t="n">
+        <v>46170</v>
       </c>
       <c r="Z215" s="3" t="n">
         <v>46170</v>
@@ -28285,10 +27892,8 @@
       <c r="X216" s="3" t="n">
         <v>46171</v>
       </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+      <c r="Y216" s="4" t="n">
+        <v>46171</v>
       </c>
       <c r="Z216" s="3" t="n">
         <v>46171</v>
@@ -28410,16 +28015,14 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>LOCACAO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA CZB9H07 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 792</t>
+          <t>LOCACAO DE VEICULO</t>
         </is>
       </c>
       <c r="X217" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y217" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr"/>
@@ -28539,16 +28142,14 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>LOCAÇÃO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA HAR1F82 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 793</t>
+          <t>LOCAÇÃO DE VEICULO</t>
         </is>
       </c>
       <c r="X218" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y218" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z218" t="inlineStr"/>
       <c r="AA218" t="inlineStr"/>
@@ -28668,16 +28269,14 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA EUS0048 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 794</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="X219" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y219" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z219" t="inlineStr"/>
       <c r="AA219" t="inlineStr"/>
@@ -28797,16 +28396,14 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA CCS0052 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 795</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="X220" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y220" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z220" t="inlineStr"/>
       <c r="AA220" t="inlineStr"/>
@@ -28926,16 +28523,14 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA DPS0050 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 796</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="X221" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y221" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z221" t="inlineStr"/>
       <c r="AA221" t="inlineStr"/>
@@ -29055,16 +28650,14 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA DPS0051 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 797</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="X222" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y222" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z222" t="inlineStr"/>
       <c r="AA222" t="inlineStr"/>
@@ -29184,16 +28777,14 @@
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>LOCACAO DE MAQUINA | REFERENTE A LOCAÇÃO DE MAQUINA PLACA ACS0049 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 798</t>
+          <t>LOCACAO DE MAQUINA</t>
         </is>
       </c>
       <c r="X223" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y223" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z223" t="inlineStr"/>
       <c r="AA223" t="inlineStr"/>
@@ -29313,16 +28904,14 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>LOCACAO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA EJZ7495 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 799</t>
+          <t>LOCACAO DE VEICULO</t>
         </is>
       </c>
       <c r="X224" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y224" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z224" t="inlineStr"/>
       <c r="AA224" t="inlineStr"/>
@@ -29442,16 +29031,14 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>LOCACAO DE VEICULO | REFERENTE A LOCAÇÃO DE VEICULO PLACA EJZ7496 - PERÍODO: 01/05/2026 A 31/05/2026 - FATURA 800</t>
+          <t>LOCACAO DE VEICULO</t>
         </is>
       </c>
       <c r="X225" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>25/06/26</t>
-        </is>
+      <c r="Y225" s="4" t="n">
+        <v>46198</v>
       </c>
       <c r="Z225" t="inlineStr"/>
       <c r="AA225" t="inlineStr"/>
@@ -29509,47 +29096,47 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1.3.1.2</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>1.3.1.2 COMERCIAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>1.3.1.2</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>1.3.1.2 COMERCIAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>7.3.1</t>
+          <t>7.5.31</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>SALARIOS</t>
+          <t>ALUGUEL ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>7.3.1 SALARIOS</t>
+          <t>7.5.31 ALUGUEL ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="R226" t="n">
@@ -29557,38 +29144,36 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>FOLHAESTAGIO042026</t>
+          <t>D260610-004</t>
         </is>
       </c>
       <c r="T226" s="2" t="n">
-        <v>2000</v>
+        <v>33750</v>
       </c>
       <c r="U226" s="2" t="n">
-        <v>-2000</v>
+        <v>-33750</v>
       </c>
       <c r="V226" s="2" t="n">
-        <v>-2000</v>
+        <v>-33750</v>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>REF FOLHA ESTAGIO COMP ABRIL 2026 | PAGTO REF FOLHA SALARIAL ESTAGIÁRIOS EDUARDO PEDRETTI E HELENA SOARES COMP ABRIL 2026.</t>
+          <t>referente a o.c 5418</t>
         </is>
       </c>
       <c r="X226" s="3" t="n">
-        <v>46147</v>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46171</v>
+      </c>
+      <c r="Y226" s="4" t="n">
+        <v>46183</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>46208</v>
+        <v>46183</v>
       </c>
       <c r="AA226" t="inlineStr"/>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>06916551000186 - RSE COMERCIO DE FERRO ACO E LOCACAO DE EQUIPAMENTOS LTD</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr"/>
@@ -29670,17 +29255,17 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>7.5.23</t>
+          <t>7.5.31</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>JUROS E MULTAS</t>
+          <t>ALUGUEL ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>7.5.23 JUROS E MULTAS</t>
+          <t>7.5.31 ALUGUEL ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="R227" t="n">
@@ -29688,38 +29273,36 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>IOF0526</t>
+          <t>D260610-005</t>
         </is>
       </c>
       <c r="T227" s="2" t="n">
-        <v>12111.4</v>
+        <v>12861.42</v>
       </c>
       <c r="U227" s="2" t="n">
-        <v>-12111.4</v>
+        <v>-12861.42</v>
       </c>
       <c r="V227" s="2" t="n">
-        <v>-12111.4</v>
+        <v>-12861.42</v>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250 | IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250</t>
+          <t>REF A OC 5417</t>
         </is>
       </c>
       <c r="X227" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46171</v>
+      </c>
+      <c r="Y227" s="4" t="n">
+        <v>46183</v>
       </c>
       <c r="Z227" s="3" t="n">
-        <v>46117</v>
+        <v>46183</v>
       </c>
       <c r="AA227" t="inlineStr"/>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>000024 - BANCO SANTANDER</t>
+          <t>06916551000186 - RSE COMERCIO DE FERRO ACO E LOCACAO DE EQUIPAMENTOS LTD</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr"/>
@@ -29801,17 +29384,17 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>7.5.22</t>
+          <t>7.11.1</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>DESPESAS BANCARIAS</t>
+          <t>OPERACOES ENTRE EMPRESAS</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>7.5.22 DESPESAS BANCARIAS</t>
+          <t>7.11.1 OPERACOES ENTRE EMPRESAS</t>
         </is>
       </c>
       <c r="R228" t="n">
@@ -29819,38 +29402,36 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>JR110526</t>
+          <t>D260615-004</t>
         </is>
       </c>
       <c r="T228" s="2" t="n">
-        <v>635</v>
+        <v>828</v>
       </c>
       <c r="U228" s="2" t="n">
-        <v>-635</v>
+        <v>-828</v>
       </c>
       <c r="V228" s="2" t="n">
-        <v>-635</v>
+        <v>-828</v>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>JUROS SALDO UTILIZ ATE LIMITE | JUROS DE UTILIZAÇÃO DE SALDO ROTATIVO DA CONTA. PERIODO 11/04 A 10/05 (CONTA NEGATIVA EM 04/05)</t>
+          <t>referente a fatura ikatec</t>
         </is>
       </c>
       <c r="X228" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y228" s="4" t="n">
+        <v>46189</v>
       </c>
       <c r="Z228" s="3" t="n">
-        <v>46331</v>
+        <v>46189</v>
       </c>
       <c r="AA228" t="inlineStr"/>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>000024 - BANCO SANTANDER</t>
+          <t>18716151000106 - IKATEC ENGENHARIA DE SOFTWARE LTDA</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr"/>
@@ -29902,47 +29483,47 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.2 COMERCIAL</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.2 COMERCIAL</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>7.5.23</t>
+          <t>7.3.1</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>JUROS E MULTAS</t>
+          <t>SALARIOS</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>7.5.23 JUROS E MULTAS</t>
+          <t>7.3.1 SALARIOS</t>
         </is>
       </c>
       <c r="R229" t="n">
@@ -29950,38 +29531,36 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>JRCG0526</t>
+          <t>FOLHAESTAGIO042026</t>
         </is>
       </c>
       <c r="T229" s="2" t="n">
-        <v>62795.35</v>
+        <v>2000</v>
       </c>
       <c r="U229" s="2" t="n">
-        <v>-62795.35</v>
+        <v>-2000</v>
       </c>
       <c r="V229" s="2" t="n">
-        <v>-62795.35</v>
+        <v>-2000</v>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250 | PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250</t>
+          <t>REF FOLHA ESTAGIO COMP ABRIL 2026</t>
         </is>
       </c>
       <c r="X229" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46147</v>
+      </c>
+      <c r="Y229" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>46117</v>
+        <v>46149</v>
       </c>
       <c r="AA229" t="inlineStr"/>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>000024 - BANCO SANTANDER</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr"/>
@@ -30063,17 +29642,17 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>7.5.9</t>
+          <t>7.5.23</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>CONSULTORIA</t>
+          <t>JUROS E MULTAS</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>7.5.9 CONSULTORIA</t>
+          <t>7.5.23 JUROS E MULTAS</t>
         </is>
       </c>
       <c r="R230" t="n">
@@ -30081,38 +29660,36 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>NF 000.000.006</t>
+          <t>IOF0526</t>
         </is>
       </c>
       <c r="T230" s="2" t="n">
-        <v>12000</v>
+        <v>12111.4</v>
       </c>
       <c r="U230" s="2" t="n">
-        <v>-12000</v>
+        <v>-12111.4</v>
       </c>
       <c r="V230" s="2" t="n">
-        <v>-12000</v>
+        <v>-12111.4</v>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000006 | [GIULIANA] REF AO SERVICOS PRESTADOS POR ANDERSON ZANUTO-SOLICITADO POR ADRIANA NOGUEIRA-COMPETENCIA 05/2026-NF 000.000.006 VALOR TOTAL R$ 12.000,00 - VENCIMENTO EM 05/06/2026-PAGAMENTO VIA TRANSFERENCIA/PIX-CHAVE PIX: 57703733000100</t>
+          <t>IOF IMPOSTO OPERACOES FINANCEIRAS CONTRATO 290000003250</t>
         </is>
       </c>
       <c r="X230" s="3" t="n">
-        <v>46167</v>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>03/06/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y230" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z230" s="3" t="n">
-        <v>46087</v>
+        <v>46146</v>
       </c>
       <c r="AA230" t="inlineStr"/>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
+          <t>000024 - BANCO SANTANDER</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr"/>
@@ -30192,19 +29769,17 @@
           <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>7.5.9</t>
-        </is>
+      <c r="O231" t="n">
+        <v>2060301</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>CONSULTORIA</t>
+          <t>ISS</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>7.5.9 CONSULTORIA</t>
+          <t>2060301 ISS</t>
         </is>
       </c>
       <c r="R231" t="n">
@@ -30212,38 +29787,34 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>NF 000.000.016</t>
+          <t>ISS052026G3S05(AM)</t>
         </is>
       </c>
       <c r="T231" s="2" t="n">
-        <v>5490</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="U231" s="2" t="n">
-        <v>-5490</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="V231" s="2" t="n">
-        <v>-5490</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000016 | PEDIDO(S) ASSOCIADO(S): [0030005386]</t>
+          <t>ISS TOMADOR RETIDO REFERENTE AO MÊS MAIO/2026 - NFS 3. PRESTAÇÃO DE SERVIÇO EM ALVARES MACHADO.</t>
         </is>
       </c>
       <c r="X231" s="3" t="n">
-        <v>46168</v>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>03/06/26</t>
-        </is>
-      </c>
-      <c r="Z231" s="3" t="n">
-        <v>46087</v>
-      </c>
+        <v>46173</v>
+      </c>
+      <c r="Y231" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="Z231" t="inlineStr"/>
       <c r="AA231" t="inlineStr"/>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>40840620000153 - SILVA &amp; FARIAS TREINAMENTOS LTDA</t>
+          <t>43206424000110 - MUNICIPIO DE ALVARES MACHADO</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr"/>
@@ -30325,17 +29896,17 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>7.5.9</t>
+          <t>7.5.22</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>CONSULTORIA</t>
+          <t>DESPESAS BANCARIAS</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>7.5.9 CONSULTORIA</t>
+          <t>7.5.22 DESPESAS BANCARIAS</t>
         </is>
       </c>
       <c r="R232" t="n">
@@ -30343,38 +29914,36 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>NF 000.000.098</t>
+          <t>JR110526</t>
         </is>
       </c>
       <c r="T232" s="2" t="n">
-        <v>1073.33</v>
+        <v>635</v>
       </c>
       <c r="U232" s="2" t="n">
-        <v>-1073.33</v>
+        <v>-635</v>
       </c>
       <c r="V232" s="2" t="n">
-        <v>-1073.33</v>
+        <v>-635</v>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000098 | PEDIDO(S) ASSOCIADO(S): [0030005388]</t>
+          <t>JUROS SALDO UTILIZ ATE LIMITE</t>
         </is>
       </c>
       <c r="X232" s="3" t="n">
-        <v>46168</v>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>03/06/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y232" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>46087</v>
+        <v>46153</v>
       </c>
       <c r="AA232" t="inlineStr"/>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>42002078000195 - CS ADMINISTRACAO E SERVICOS LTDA</t>
+          <t>000024 - BANCO SANTANDER</t>
         </is>
       </c>
       <c r="AC232" t="inlineStr"/>
@@ -30456,17 +30025,17 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>7.5.9</t>
+          <t>7.5.23</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>CONSULTORIA</t>
+          <t>JUROS E MULTAS</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>7.5.9 CONSULTORIA</t>
+          <t>7.5.23 JUROS E MULTAS</t>
         </is>
       </c>
       <c r="R233" t="n">
@@ -30474,38 +30043,36 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>NF 000.000.205</t>
+          <t>JRCG0526</t>
         </is>
       </c>
       <c r="T233" s="2" t="n">
-        <v>1149.06</v>
+        <v>62795.35</v>
       </c>
       <c r="U233" s="2" t="n">
-        <v>-1149.06</v>
+        <v>-62795.35</v>
       </c>
       <c r="V233" s="2" t="n">
-        <v>-1149.06</v>
+        <v>-62795.35</v>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000000205 | PEDIDO(S) ASSOCIADO(S): [0030005382]</t>
+          <t>PREST. DE EMPREST. FINANCIAMENTO CONTRATO 290000003250</t>
         </is>
       </c>
       <c r="X233" s="3" t="n">
-        <v>46164</v>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>03/06/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y233" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z233" s="3" t="n">
-        <v>46087</v>
+        <v>46146</v>
       </c>
       <c r="AA233" t="inlineStr"/>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>39933208000107 - H B BOSSOLANI SERVICOS ADMINISTRATIVOS</t>
+          <t>000024 - BANCO SANTANDER</t>
         </is>
       </c>
       <c r="AC233" t="inlineStr"/>
@@ -30557,47 +30124,47 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1.3.1.3</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>OPERACIONAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>1.3.1.3 OPERACIONAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>1.3.1.3</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>OPERACIONAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>1.3.1.3 OPERACIONAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>7.5.5</t>
+          <t>7.5.9</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>MATERIAL DE ESCRITORIO</t>
+          <t>CONSULTORIA</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>7.5.5 MATERIAL DE ESCRITORIO</t>
+          <t>7.5.9 CONSULTORIA</t>
         </is>
       </c>
       <c r="R234" t="n">
@@ -30605,38 +30172,36 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>PED-0067386001</t>
+          <t>NF 000.000.006</t>
         </is>
       </c>
       <c r="T234" s="2" t="n">
-        <v>93.39</v>
+        <v>12000</v>
       </c>
       <c r="U234" s="2" t="n">
-        <v>-93.39</v>
+        <v>-12000</v>
       </c>
       <c r="V234" s="2" t="n">
-        <v>-93.39</v>
+        <v>-12000</v>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>REFERENTE A NF 000025823 | PEDIDO(S) ASSOCIADO(S): [0030005354] Cristina - Compra de material utilizado para cano que foi danificado durante o conserto da área afetada pelo deslizamento do barranco. NF 25823 - BOLETO 13/05</t>
+          <t>REFERENTE A NF 000000006</t>
         </is>
       </c>
       <c r="X234" s="3" t="n">
-        <v>46027</v>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>13/05/26</t>
-        </is>
+        <v>46167</v>
+      </c>
+      <c r="Y234" s="4" t="n">
+        <v>46176</v>
       </c>
       <c r="Z234" s="3" t="n">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="AA234" t="inlineStr"/>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>57832180000195 - NELBRA MATERIAIS PARA CONSTRUCAO LTDA</t>
+          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
         </is>
       </c>
       <c r="AC234" t="inlineStr"/>
@@ -30688,47 +30253,47 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>1.3.1.3</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>OPERACIONAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>1.3.1.3 OPERACIONAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>1.3.1.3</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>OPERACIONAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>1.3.1.3 OPERACIONAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>7.3.21</t>
+          <t>7.5.9</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>RESCISOES</t>
+          <t>CONSULTORIA</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>7.3.21 RESCISOES</t>
+          <t>7.5.9 CONSULTORIA</t>
         </is>
       </c>
       <c r="R235" t="n">
@@ -30736,38 +30301,36 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>PENSÃOG3S050426</t>
+          <t>NF 000.000.016</t>
         </is>
       </c>
       <c r="T235" s="2" t="n">
-        <v>500</v>
+        <v>5490</v>
       </c>
       <c r="U235" s="2" t="n">
-        <v>-500</v>
+        <v>-5490</v>
       </c>
       <c r="V235" s="2" t="n">
-        <v>-500</v>
+        <v>-5490</v>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>REF PENSÃO FILHA FUNCIONARIO COMP ABRIL 2026 | PAGTO REF CRÉDITO DE PENSÃO ALIMENTÍCIA FILHA FUNCIONARIO LUIS HENRIQUE SEMENSATO COMP ABRIL 2026. RENATA PERES NUNES: CPF: 371.144.288-98 // BANCO: ITAÚ // AGÊNCIA: 0203 // CONTA: 64310-1 // CHAVE PIX: re.pnunes6@gmail.com</t>
+          <t>REFERENTE A NF 000000016</t>
         </is>
       </c>
       <c r="X235" s="3" t="n">
-        <v>46147</v>
-      </c>
-      <c r="Y235" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46168</v>
+      </c>
+      <c r="Y235" s="4" t="n">
+        <v>46176</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>46208</v>
+        <v>46176</v>
       </c>
       <c r="AA235" t="inlineStr"/>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>37114428898 - RENATA PERES NUNES</t>
+          <t>40840620000153 - SILVA &amp; FARIAS TREINAMENTOS LTDA</t>
         </is>
       </c>
       <c r="AC235" t="inlineStr"/>
@@ -30849,17 +30412,17 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>7.3.1</t>
+          <t>7.5.9</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>SALARIOS</t>
+          <t>CONSULTORIA</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>7.3.1 SALARIOS</t>
+          <t>7.5.9 CONSULTORIA</t>
         </is>
       </c>
       <c r="R236" t="n">
@@ -30867,38 +30430,36 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>PIXANIVERSARIO0526</t>
+          <t>NF 000.000.098</t>
         </is>
       </c>
       <c r="T236" s="2" t="n">
-        <v>150</v>
+        <v>1073.33</v>
       </c>
       <c r="U236" s="2" t="n">
-        <v>-150</v>
+        <v>-1073.33</v>
       </c>
       <c r="V236" s="2" t="n">
-        <v>-150</v>
+        <v>-1073.33</v>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA  AP LIMA QUEIRÓZ | PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA APARECIDA LIMA QUEIROZ Agência 0337 Banco caixa Conta poupança 765383386-2 Chave Pix CPF 44533028861</t>
+          <t>REFERENTE A NF 000000098</t>
         </is>
       </c>
       <c r="X236" s="3" t="n">
-        <v>46170</v>
-      </c>
-      <c r="Y236" t="inlineStr">
-        <is>
-          <t>28/05/26</t>
-        </is>
+        <v>46168</v>
+      </c>
+      <c r="Y236" s="4" t="n">
+        <v>46176</v>
       </c>
       <c r="Z236" s="3" t="n">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="AA236" t="inlineStr"/>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>42002078000195 - CS ADMINISTRACAO E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="AC236" t="inlineStr"/>
@@ -30980,17 +30541,17 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>7.3.21</t>
+          <t>7.5.9</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>RESCISOES</t>
+          <t>CONSULTORIA</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>7.3.21 RESCISOES</t>
+          <t>7.5.9 CONSULTORIA</t>
         </is>
       </c>
       <c r="R237" t="n">
@@ -30998,38 +30559,36 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>RESCISÃOESTAGIO052</t>
+          <t>NF 000.000.205</t>
         </is>
       </c>
       <c r="T237" s="2" t="n">
-        <v>1683.33</v>
+        <v>1149.06</v>
       </c>
       <c r="U237" s="2" t="n">
-        <v>-1683.33</v>
+        <v>-1149.06</v>
       </c>
       <c r="V237" s="2" t="n">
-        <v>-1683.33</v>
+        <v>-1149.06</v>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 - HELENA | PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 HELENA SOARES GOES DA SILVA BANCO C6 BANK AG 0001 C/C 38210981-3 PIX 50500800880</t>
+          <t>REFERENTE A NF 000000205</t>
         </is>
       </c>
       <c r="X237" s="3" t="n">
-        <v>46170</v>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+        <v>46164</v>
+      </c>
+      <c r="Y237" s="4" t="n">
+        <v>46176</v>
       </c>
       <c r="Z237" s="3" t="n">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="AA237" t="inlineStr"/>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>39933208000107 - H B BOSSOLANI SERVICOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="AC237" t="inlineStr"/>
@@ -31081,47 +30640,47 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>OPERACIONAL</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.3 OPERACIONAL</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>OPERACIONAL</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.3 OPERACIONAL</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>7.3.21</t>
+          <t>7.5.5</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>RESCISOES</t>
+          <t>MATERIAL DE ESCRITORIO</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>7.3.21 RESCISOES</t>
+          <t>7.5.5 MATERIAL DE ESCRITORIO</t>
         </is>
       </c>
       <c r="R238" t="n">
@@ -31129,38 +30688,36 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>RESCSISÃOMAIO26</t>
+          <t>PED-0067386001</t>
         </is>
       </c>
       <c r="T238" s="2" t="n">
-        <v>650</v>
+        <v>93.39</v>
       </c>
       <c r="U238" s="2" t="n">
-        <v>-650</v>
+        <v>-93.39</v>
       </c>
       <c r="V238" s="2" t="n">
-        <v>-650</v>
+        <v>-93.39</v>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26 | PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26 - EDUARDO PEDRETTI ARRUDA RONCHESEL - ESTAGIO FINANCEIRO - BANCO INTER AG 0001 - C/C 18992669-4 - PIX 18997314402</t>
+          <t>REFERENTE A NF 000025823</t>
         </is>
       </c>
       <c r="X238" s="3" t="n">
-        <v>46160</v>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+        <v>46143</v>
+      </c>
+      <c r="Y238" s="4" t="n">
+        <v>46155</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="AA238" t="inlineStr"/>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
+          <t>57832180000195 - NELBRA MATERIAIS PARA CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr"/>
@@ -31212,47 +30769,47 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>1.3.1.2</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>OPERACIONAL</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>1.3.1.2 COMERCIAL</t>
+          <t>1.3.1.3 OPERACIONAL</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>1.3.1.2</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>OPERACIONAL</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>1.3.1.2 COMERCIAL</t>
+          <t>1.3.1.3 OPERACIONAL</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>7.1.8</t>
+          <t>7.3.21</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>DESPESAS DE VIAGEM</t>
+          <t>RESCISOES</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>7.1.8 DESPESAS DE VIAGEM</t>
+          <t>7.3.21 RESCISOES</t>
         </is>
       </c>
       <c r="R239" t="n">
@@ -31260,38 +30817,36 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>RKM05052026</t>
+          <t>PENSÃOG3S050426</t>
         </is>
       </c>
       <c r="T239" s="2" t="n">
-        <v>1184.9</v>
+        <v>500</v>
       </c>
       <c r="U239" s="2" t="n">
-        <v>-1184.9</v>
+        <v>-500</v>
       </c>
       <c r="V239" s="2" t="n">
-        <v>-1184.9</v>
+        <v>-500</v>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>REEMBOLSO ANDERSON ZANUTO | REFERENTE AO RELATORIO DE REEMBOLSO POR QUILOMETRAGEM DO ANDERSON ZANUTO NO PERÍODO DE 02/04/2026 A 29/04/2026 PAGAMENTO VIA TRANSFERENCIA/PIX CHAVE PIX: 57703733000100</t>
+          <t>REF PENSÃO FILHA FUNCIONARIO COMP ABRIL 2026</t>
         </is>
       </c>
       <c r="X239" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>05/05/26</t>
-        </is>
+      <c r="Y239" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z239" s="3" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="AA239" t="inlineStr"/>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
+          <t>37114428898 - RENATA PERES NUNES</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr"/>
@@ -31373,17 +30928,17 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>7.3.9</t>
+          <t>7.3.1</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>SEGURANCA DO TRABALHO</t>
+          <t>SALARIOS</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>7.3.9 SEGURANCA DO TRABALHO</t>
+          <t>7.3.1 SALARIOS</t>
         </is>
       </c>
       <c r="R240" t="n">
@@ -31391,38 +30946,36 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>SEGUROVIDAG3S0426</t>
+          <t>PIXANIVERSARIO0526</t>
         </is>
       </c>
       <c r="T240" s="2" t="n">
-        <v>510.43</v>
+        <v>150</v>
       </c>
       <c r="U240" s="2" t="n">
-        <v>-510.43</v>
+        <v>-150</v>
       </c>
       <c r="V240" s="2" t="n">
-        <v>-510.43</v>
+        <v>-150</v>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>REF SEGURO DE VIDA COMP MAIO 2026 | PAGTO REF SEGURO DE VIDA FUNCIONARIOS COMP MAIO 2026.</t>
+          <t>PAGTO REF A PIX ANIVERSARIO COMPETENCIA MAIO 2026 - FUNCIONARIA LARISSA  AP LIMA QUEIRÓZ</t>
         </is>
       </c>
       <c r="X240" s="3" t="n">
-        <v>46164</v>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+        <v>46170</v>
+      </c>
+      <c r="Y240" s="4" t="n">
+        <v>46170</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="AA240" t="inlineStr"/>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>42283770000139 - ICATU SEGUROS S/A</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr"/>
@@ -31474,47 +31027,47 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>1.3.1.2</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>1.3.1.2 COMERCIAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>1.3.1.2</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>COMERCIAL</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>1.3.1.2 COMERCIAL</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>7.3.10</t>
+          <t>7.3.21</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>TRANSPORTE DE COLABORADORES</t>
+          <t>RESCISOES</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>7.3.10 TRANSPORTE DE COLABORADORES</t>
+          <t>7.3.21 RESCISOES</t>
         </is>
       </c>
       <c r="R241" t="n">
@@ -31522,38 +31075,36 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>SEMPARARG3S050526</t>
+          <t>RESCISÃOESTAGIO052</t>
         </is>
       </c>
       <c r="T241" s="2" t="n">
-        <v>10437.74</v>
+        <v>1683.33</v>
       </c>
       <c r="U241" s="2" t="n">
-        <v>-10437.74</v>
+        <v>-1683.33</v>
       </c>
       <c r="V241" s="2" t="n">
-        <v>-10437.74</v>
+        <v>-1683.33</v>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>REF SEM PARAR COMP MAIO 2026 | PAGTO REF MENSALIDADE BENEFICIO SEM PARAR COMPETENCIA MAIO 2026.</t>
+          <t>PAGTO REF A ACERTO RESCISÃO ESTAGIARIA COMPETENCIA MAIO 2026 - HELENA</t>
         </is>
       </c>
       <c r="X241" s="3" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+        <v>46170</v>
+      </c>
+      <c r="Y241" s="4" t="n">
+        <v>46171</v>
       </c>
       <c r="Z241" s="3" t="n">
-        <v>46167</v>
+        <v>46171</v>
       </c>
       <c r="AA241" t="inlineStr"/>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>00288916001080 - VB-SERVICOS COMERCIO E ADMINISTRACAO LTDA</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="AC241" t="inlineStr"/>
@@ -31605,47 +31156,47 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>1.3.1.4</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>LOGISTICA</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>1.3.1.4 LOGISTICA</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>1.3.1.4</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>LOGISTICA</t>
+          <t>ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>1.3.1.4 LOGISTICA</t>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>7.3.13</t>
+          <t>7.3.21</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>SINDICATOS</t>
+          <t>RESCISOES</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>7.3.13 SINDICATOS</t>
+          <t>7.3.21 RESCISOES</t>
         </is>
       </c>
       <c r="R242" t="n">
@@ -31653,38 +31204,36 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>SINDICATOG3S04261</t>
+          <t>RESCSISÃOMAIO26</t>
         </is>
       </c>
       <c r="T242" s="2" t="n">
-        <v>108.96</v>
+        <v>650</v>
       </c>
       <c r="U242" s="2" t="n">
-        <v>-108.96</v>
+        <v>-650</v>
       </c>
       <c r="V242" s="2" t="n">
-        <v>-108.96</v>
+        <v>-650</v>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>REF SINDICATO COMP ABRIL 2026. | PAGTO REF SINDICATO CONTRIBUIÇÃO NEGOCIAL DESCONTO EM FOLHA COMP ABRIL 2026.</t>
+          <t>PAGTO REF A ACERTO RESCISÃO BOLSA ESTAGIO COMPETENCIA MAIO 26</t>
         </is>
       </c>
       <c r="X242" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>10/05/26</t>
-        </is>
+        <v>46160</v>
+      </c>
+      <c r="Y242" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>46331</v>
+        <v>46160</v>
       </c>
       <c r="AA242" t="inlineStr"/>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>11432305000199 - SINDICATO DOS TRAB. TRANSP. TERRESTRES DE PRES. PRUDENT</t>
+          <t>209477332000519 - G3S COMER E IND DE FERRO E ACO LTDA - FILIAL</t>
         </is>
       </c>
       <c r="AC242" t="inlineStr"/>
@@ -31736,47 +31285,47 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.2 COMERCIAL</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.2 COMERCIAL</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>7.3.13</t>
+          <t>7.1.8</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>SINDICATOS</t>
+          <t>DESPESAS DE VIAGEM</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>7.3.13 SINDICATOS</t>
+          <t>7.1.8 DESPESAS DE VIAGEM</t>
         </is>
       </c>
       <c r="R243" t="n">
@@ -31784,38 +31333,36 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>SINDICATOG3S050426</t>
+          <t>RKM05052026</t>
         </is>
       </c>
       <c r="T243" s="2" t="n">
-        <v>445.71</v>
+        <v>1184.9</v>
       </c>
       <c r="U243" s="2" t="n">
-        <v>-445.71</v>
+        <v>-1184.9</v>
       </c>
       <c r="V243" s="2" t="n">
-        <v>-445.71</v>
+        <v>-1184.9</v>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>REF SINDICATO COMP ABRIL 2026. | PAGTO REF SINDICATO CONTRIBUIÇÃO ASSISTENCIAL DESCONTO EM FOLHA COMP ABRIL 2026.</t>
+          <t>REEMBOLSO ANDERSON ZANUTO</t>
         </is>
       </c>
       <c r="X243" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46147</v>
+      </c>
+      <c r="Y243" s="4" t="n">
+        <v>46147</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>46331</v>
+        <v>46147</v>
       </c>
       <c r="AA243" t="inlineStr"/>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>55354849000155 - SINDICATO EMPREGADOS COMERCIO DE PRESIDENTE PRUDEN</t>
+          <t>57703733000100 - 57.703.733 ANDERSON ZANUTO</t>
         </is>
       </c>
       <c r="AC243" t="inlineStr"/>
@@ -31897,17 +31444,17 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>7.5.22</t>
+          <t>7.3.9</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>DESPESAS BANCARIAS</t>
+          <t>SEGURANCA DO TRABALHO</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>7.5.22 DESPESAS BANCARIAS</t>
+          <t>7.3.9 SEGURANCA DO TRABALHO</t>
         </is>
       </c>
       <c r="R244" t="n">
@@ -31915,38 +31462,36 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>TAR040526</t>
+          <t>SEGUROVIDAG3S0426</t>
         </is>
       </c>
       <c r="T244" s="2" t="n">
-        <v>41.4</v>
+        <v>510.43</v>
       </c>
       <c r="U244" s="2" t="n">
-        <v>-41.4</v>
+        <v>-510.43</v>
       </c>
       <c r="V244" s="2" t="n">
-        <v>-41.4</v>
+        <v>-510.43</v>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES</t>
+          <t>REF SEGURO DE VIDA COMP MAIO 2026</t>
         </is>
       </c>
       <c r="X244" s="3" t="n">
-        <v>46117</v>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>04/05/26</t>
-        </is>
+        <v>46164</v>
+      </c>
+      <c r="Y244" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z244" s="3" t="n">
-        <v>46117</v>
+        <v>46167</v>
       </c>
       <c r="AA244" t="inlineStr"/>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>42283770000139 - ICATU SEGUROS S/A</t>
         </is>
       </c>
       <c r="AC244" t="inlineStr"/>
@@ -31998,47 +31543,47 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.2 COMERCIAL</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>COMERCIAL</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.2 COMERCIAL</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>7.5.22</t>
+          <t>7.3.10</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>DESPESAS BANCARIAS</t>
+          <t>TRANSPORTE DE COLABORADORES</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>7.5.22 DESPESAS BANCARIAS</t>
+          <t>7.3.10 TRANSPORTE DE COLABORADORES</t>
         </is>
       </c>
       <c r="R245" t="n">
@@ -32046,38 +31591,36 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>TAR050526</t>
+          <t>SEMPARARG3S050526</t>
         </is>
       </c>
       <c r="T245" s="2" t="n">
-        <v>6.3</v>
+        <v>10437.74</v>
       </c>
       <c r="U245" s="2" t="n">
-        <v>-6.3</v>
+        <v>-10437.74</v>
       </c>
       <c r="V245" s="2" t="n">
-        <v>-6.3</v>
+        <v>-10437.74</v>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES</t>
+          <t>REF SEM PARAR COMP MAIO 2026</t>
         </is>
       </c>
       <c r="X245" s="3" t="n">
-        <v>46147</v>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>05/05/26</t>
-        </is>
+        <v>46162</v>
+      </c>
+      <c r="Y245" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z245" s="3" t="n">
-        <v>46147</v>
+        <v>46167</v>
       </c>
       <c r="AA245" t="inlineStr"/>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>00288916001080 - VB-SERVICOS COMERCIO E ADMINISTRACAO LTDA</t>
         </is>
       </c>
       <c r="AC245" t="inlineStr"/>
@@ -32129,47 +31672,47 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.4</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>LOGISTICA</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.4 LOGISTICA</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>1.3.1.1</t>
+          <t>1.3.1.4</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>ADMINISTRATIVO</t>
+          <t>LOGISTICA</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>1.3.1.1 ADMINISTRATIVO</t>
+          <t>1.3.1.4 LOGISTICA</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>7.5.22</t>
+          <t>7.3.13</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>DESPESAS BANCARIAS</t>
+          <t>SINDICATOS</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>7.5.22 DESPESAS BANCARIAS</t>
+          <t>7.3.13 SINDICATOS</t>
         </is>
       </c>
       <c r="R246" t="n">
@@ -32177,38 +31720,36 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>TAR060526</t>
+          <t>SINDICATOG3S04261</t>
         </is>
       </c>
       <c r="T246" s="2" t="n">
-        <v>14.4</v>
+        <v>108.96</v>
       </c>
       <c r="U246" s="2" t="n">
-        <v>-14.4</v>
+        <v>-108.96</v>
       </c>
       <c r="V246" s="2" t="n">
-        <v>-14.4</v>
+        <v>-108.96</v>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES</t>
+          <t>REF SINDICATO COMP ABRIL 2026.</t>
         </is>
       </c>
       <c r="X246" s="3" t="n">
-        <v>46178</v>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>06/05/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y246" s="4" t="n">
+        <v>46152</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>46178</v>
+        <v>46153</v>
       </c>
       <c r="AA246" t="inlineStr"/>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>11432305000199 - SINDICATO DOS TRAB. TRANSP. TERRESTRES DE PRES. PRUDENT</t>
         </is>
       </c>
       <c r="AC246" t="inlineStr"/>
@@ -32290,17 +31831,17 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>7.5.22</t>
+          <t>7.3.13</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>DESPESAS BANCARIAS</t>
+          <t>SINDICATOS</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>7.5.22 DESPESAS BANCARIAS</t>
+          <t>7.3.13 SINDICATOS</t>
         </is>
       </c>
       <c r="R247" t="n">
@@ -32308,38 +31849,36 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>TAR070526</t>
+          <t>SINDICATOG3S050426</t>
         </is>
       </c>
       <c r="T247" s="2" t="n">
-        <v>4.5</v>
+        <v>445.71</v>
       </c>
       <c r="U247" s="2" t="n">
-        <v>-4.5</v>
+        <v>-445.71</v>
       </c>
       <c r="V247" s="2" t="n">
-        <v>-4.5</v>
+        <v>-445.71</v>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES</t>
+          <t>REF SINDICATO COMP ABRIL 2026.</t>
         </is>
       </c>
       <c r="X247" s="3" t="n">
-        <v>46208</v>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>07/05/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y247" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z247" s="3" t="n">
-        <v>46208</v>
+        <v>46153</v>
       </c>
       <c r="AA247" t="inlineStr"/>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>5419 - COOPERATIVA SICREDI</t>
+          <t>55354849000155 - SINDICATO EMPREGADOS COMERCIO DE PRESIDENTE PRUDEN</t>
         </is>
       </c>
       <c r="AC247" t="inlineStr"/>
@@ -32439,33 +31978,31 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>TAR080526</t>
+          <t>TAR040526</t>
         </is>
       </c>
       <c r="T248" s="2" t="n">
-        <v>17.1</v>
+        <v>41.4</v>
       </c>
       <c r="U248" s="2" t="n">
-        <v>-17.1</v>
+        <v>-41.4</v>
       </c>
       <c r="V248" s="2" t="n">
-        <v>-17.1</v>
+        <v>-41.4</v>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 46 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X248" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>08/05/26</t>
-        </is>
+        <v>46146</v>
+      </c>
+      <c r="Y248" s="4" t="n">
+        <v>46146</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>46239</v>
+        <v>46146</v>
       </c>
       <c r="AA248" t="inlineStr"/>
       <c r="AB248" t="inlineStr">
@@ -32570,33 +32107,31 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>TAR110526</t>
+          <t>TAR050526</t>
         </is>
       </c>
       <c r="T249" s="2" t="n">
-        <v>36</v>
+        <v>6.3</v>
       </c>
       <c r="U249" s="2" t="n">
-        <v>-36</v>
+        <v>-6.3</v>
       </c>
       <c r="V249" s="2" t="n">
-        <v>-36</v>
+        <v>-6.3</v>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 07 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X249" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>11/05/26</t>
-        </is>
+        <v>46147</v>
+      </c>
+      <c r="Y249" s="4" t="n">
+        <v>46147</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>46331</v>
+        <v>46147</v>
       </c>
       <c r="AA249" t="inlineStr"/>
       <c r="AB249" t="inlineStr">
@@ -32701,33 +32236,31 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>TAR12052026</t>
+          <t>TAR060526</t>
         </is>
       </c>
       <c r="T250" s="2" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="U250" s="2" t="n">
-        <v>-0.1</v>
+        <v>-14.4</v>
       </c>
       <c r="V250" s="2" t="n">
-        <v>-0.1</v>
+        <v>-14.4</v>
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>TARIFA BAIXA DE TITULOS | TARIFA BAIXA DE TITULOS</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 16 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X250" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>12/05/26</t>
-        </is>
+        <v>46148</v>
+      </c>
+      <c r="Y250" s="4" t="n">
+        <v>46148</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>46361</v>
+        <v>46148</v>
       </c>
       <c r="AA250" t="inlineStr"/>
       <c r="AB250" t="inlineStr">
@@ -32832,33 +32365,31 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>TAR120526</t>
+          <t>TAR070526</t>
         </is>
       </c>
       <c r="T251" s="2" t="n">
-        <v>10.8</v>
+        <v>4.5</v>
       </c>
       <c r="U251" s="2" t="n">
-        <v>-10.8</v>
+        <v>-4.5</v>
       </c>
       <c r="V251" s="2" t="n">
-        <v>-10.8</v>
+        <v>-4.5</v>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 05 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X251" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>12/05/26</t>
-        </is>
+        <v>46149</v>
+      </c>
+      <c r="Y251" s="4" t="n">
+        <v>46149</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>46361</v>
+        <v>46149</v>
       </c>
       <c r="AA251" t="inlineStr"/>
       <c r="AB251" t="inlineStr">
@@ -32963,33 +32494,31 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>TAR130526</t>
+          <t>TAR080526</t>
         </is>
       </c>
       <c r="T252" s="2" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="U252" s="2" t="n">
-        <v>-11.7</v>
+        <v>-17.1</v>
       </c>
       <c r="V252" s="2" t="n">
-        <v>-11.7</v>
+        <v>-17.1</v>
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 19 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X252" s="3" t="n">
-        <v>46155</v>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>13/05/26</t>
-        </is>
+        <v>46150</v>
+      </c>
+      <c r="Y252" s="4" t="n">
+        <v>46150</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>46155</v>
+        <v>46150</v>
       </c>
       <c r="AA252" t="inlineStr"/>
       <c r="AB252" t="inlineStr">
@@ -33094,33 +32623,31 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>TAR14052026</t>
+          <t>TAR110526</t>
         </is>
       </c>
       <c r="T253" s="2" t="n">
-        <v>0.1</v>
+        <v>36</v>
       </c>
       <c r="U253" s="2" t="n">
-        <v>-0.1</v>
+        <v>-36</v>
       </c>
       <c r="V253" s="2" t="n">
-        <v>-0.1</v>
+        <v>-36</v>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>TARIFA BAIXA DE TITULOS | TARIFA BAIXA DE TITULOS</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 40 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X253" s="3" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>14/05/26</t>
-        </is>
+        <v>46153</v>
+      </c>
+      <c r="Y253" s="4" t="n">
+        <v>46153</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="AA253" t="inlineStr"/>
       <c r="AB253" t="inlineStr">
@@ -33225,33 +32752,31 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>TAR140526</t>
+          <t>TAR12052026</t>
         </is>
       </c>
       <c r="T254" s="2" t="n">
-        <v>9.9</v>
+        <v>0.1</v>
       </c>
       <c r="U254" s="2" t="n">
-        <v>-9.9</v>
+        <v>-0.1</v>
       </c>
       <c r="V254" s="2" t="n">
-        <v>-9.9</v>
+        <v>-0.1</v>
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA BAIXA DE TITULOS</t>
         </is>
       </c>
       <c r="X254" s="3" t="n">
-        <v>46156</v>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>14/05/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y254" s="4" t="n">
+        <v>46154</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="AA254" t="inlineStr"/>
       <c r="AB254" t="inlineStr">
@@ -33356,33 +32881,31 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>TAR150526</t>
+          <t>TAR120526</t>
         </is>
       </c>
       <c r="T255" s="2" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="U255" s="2" t="n">
-        <v>-15.3</v>
+        <v>-10.8</v>
       </c>
       <c r="V255" s="2" t="n">
-        <v>-15.3</v>
+        <v>-10.8</v>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 12 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X255" s="3" t="n">
-        <v>46157</v>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46154</v>
+      </c>
+      <c r="Y255" s="4" t="n">
+        <v>46154</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="AA255" t="inlineStr"/>
       <c r="AB255" t="inlineStr">
@@ -33487,33 +33010,31 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>TAR180526</t>
+          <t>TAR130526</t>
         </is>
       </c>
       <c r="T256" s="2" t="n">
-        <v>27</v>
+        <v>11.7</v>
       </c>
       <c r="U256" s="2" t="n">
-        <v>-27</v>
+        <v>-11.7</v>
       </c>
       <c r="V256" s="2" t="n">
-        <v>-27</v>
+        <v>-11.7</v>
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X256" s="3" t="n">
-        <v>46160</v>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>18/05/26</t>
-        </is>
+        <v>46155</v>
+      </c>
+      <c r="Y256" s="4" t="n">
+        <v>46155</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="AA256" t="inlineStr"/>
       <c r="AB256" t="inlineStr">
@@ -33618,33 +33139,31 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>TAR190526</t>
+          <t>TAR14052026</t>
         </is>
       </c>
       <c r="T257" s="2" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="U257" s="2" t="n">
-        <v>-8.1</v>
+        <v>-0.1</v>
       </c>
       <c r="V257" s="2" t="n">
-        <v>-8.1</v>
+        <v>-0.1</v>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
+          <t>TARIFA BAIXA DE TITULOS</t>
         </is>
       </c>
       <c r="X257" s="3" t="n">
-        <v>46161</v>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>19/05/26</t>
-        </is>
+        <v>46156</v>
+      </c>
+      <c r="Y257" s="4" t="n">
+        <v>46156</v>
       </c>
       <c r="Z257" s="3" t="n">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="AA257" t="inlineStr"/>
       <c r="AB257" t="inlineStr">
@@ -33749,33 +33268,31 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>TAR200526</t>
+          <t>TAR140526</t>
         </is>
       </c>
       <c r="T258" s="2" t="n">
-        <v>18</v>
+        <v>9.9</v>
       </c>
       <c r="U258" s="2" t="n">
-        <v>-18</v>
+        <v>-9.9</v>
       </c>
       <c r="V258" s="2" t="n">
-        <v>-18</v>
+        <v>-9.9</v>
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X258" s="3" t="n">
-        <v>46162</v>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>20/05/26</t>
-        </is>
+        <v>46156</v>
+      </c>
+      <c r="Y258" s="4" t="n">
+        <v>46156</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="AA258" t="inlineStr"/>
       <c r="AB258" t="inlineStr">
@@ -33880,33 +33397,31 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>TAR210526</t>
+          <t>TAR150526</t>
         </is>
       </c>
       <c r="T259" s="2" t="n">
-        <v>8.1</v>
+        <v>15.3</v>
       </c>
       <c r="U259" s="2" t="n">
-        <v>-8.1</v>
+        <v>-15.3</v>
       </c>
       <c r="V259" s="2" t="n">
-        <v>-8.1</v>
+        <v>-15.3</v>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 17 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X259" s="3" t="n">
-        <v>46163</v>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>21/05/26</t>
-        </is>
+        <v>46157</v>
+      </c>
+      <c r="Y259" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="Z259" s="3" t="n">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="AA259" t="inlineStr"/>
       <c r="AB259" t="inlineStr">
@@ -34011,33 +33526,31 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>TAR220526</t>
+          <t>TAR180526</t>
         </is>
       </c>
       <c r="T260" s="2" t="n">
-        <v>16.2</v>
+        <v>27</v>
       </c>
       <c r="U260" s="2" t="n">
-        <v>-16.2</v>
+        <v>-27</v>
       </c>
       <c r="V260" s="2" t="n">
-        <v>-16.2</v>
+        <v>-27</v>
       </c>
       <c r="W260" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 30 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X260" s="3" t="n">
-        <v>46164</v>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>22/05/26</t>
-        </is>
+        <v>46160</v>
+      </c>
+      <c r="Y260" s="4" t="n">
+        <v>46160</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="AA260" t="inlineStr"/>
       <c r="AB260" t="inlineStr">
@@ -34142,33 +33655,31 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>TAR250526</t>
+          <t>TAR190526</t>
         </is>
       </c>
       <c r="T261" s="2" t="n">
-        <v>31.5</v>
+        <v>8.1</v>
       </c>
       <c r="U261" s="2" t="n">
-        <v>-31.5</v>
+        <v>-8.1</v>
       </c>
       <c r="V261" s="2" t="n">
-        <v>-31.5</v>
+        <v>-8.1</v>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X261" s="3" t="n">
-        <v>46167</v>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>25/05/26</t>
-        </is>
+        <v>46161</v>
+      </c>
+      <c r="Y261" s="4" t="n">
+        <v>46161</v>
       </c>
       <c r="Z261" s="3" t="n">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="AA261" t="inlineStr"/>
       <c r="AB261" t="inlineStr">
@@ -34273,33 +33784,31 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>TAR260526</t>
+          <t>TAR200526</t>
         </is>
       </c>
       <c r="T262" s="2" t="n">
-        <v>11.7</v>
+        <v>18</v>
       </c>
       <c r="U262" s="2" t="n">
-        <v>-11.7</v>
+        <v>-18</v>
       </c>
       <c r="V262" s="2" t="n">
-        <v>-11.7</v>
+        <v>-18</v>
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 20 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X262" s="3" t="n">
-        <v>46168</v>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>26/05/26</t>
-        </is>
+        <v>46162</v>
+      </c>
+      <c r="Y262" s="4" t="n">
+        <v>46162</v>
       </c>
       <c r="Z262" s="3" t="n">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="AA262" t="inlineStr"/>
       <c r="AB262" t="inlineStr">
@@ -34404,33 +33913,31 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>TAR270526</t>
+          <t>TAR210526</t>
         </is>
       </c>
       <c r="T263" s="2" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="U263" s="2" t="n">
-        <v>-9.9</v>
+        <v>-8.1</v>
       </c>
       <c r="V263" s="2" t="n">
-        <v>-9.9</v>
+        <v>-8.1</v>
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 09 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X263" s="3" t="n">
-        <v>46169</v>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>27/05/26</t>
-        </is>
+        <v>46163</v>
+      </c>
+      <c r="Y263" s="4" t="n">
+        <v>46163</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="AA263" t="inlineStr"/>
       <c r="AB263" t="inlineStr">
@@ -34535,33 +34042,31 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>TAR280526</t>
+          <t>TAR220526</t>
         </is>
       </c>
       <c r="T264" s="2" t="n">
-        <v>9.9</v>
+        <v>16.2</v>
       </c>
       <c r="U264" s="2" t="n">
-        <v>-9.9</v>
+        <v>-16.2</v>
       </c>
       <c r="V264" s="2" t="n">
-        <v>-9.9</v>
+        <v>-16.2</v>
       </c>
       <c r="W264" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 18 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X264" s="3" t="n">
-        <v>46170</v>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>28/05/26</t>
-        </is>
+        <v>46164</v>
+      </c>
+      <c r="Y264" s="4" t="n">
+        <v>46164</v>
       </c>
       <c r="Z264" s="3" t="n">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="AA264" t="inlineStr"/>
       <c r="AB264" t="inlineStr">
@@ -34666,33 +34171,31 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>TAR290526</t>
+          <t>TAR250526</t>
         </is>
       </c>
       <c r="T265" s="2" t="n">
-        <v>23.4</v>
+        <v>31.5</v>
       </c>
       <c r="U265" s="2" t="n">
-        <v>-23.4</v>
+        <v>-31.5</v>
       </c>
       <c r="V265" s="2" t="n">
-        <v>-23.4</v>
+        <v>-31.5</v>
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES | TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 35 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X265" s="3" t="n">
-        <v>46171</v>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>29/05/26</t>
-        </is>
+        <v>46167</v>
+      </c>
+      <c r="Y265" s="4" t="n">
+        <v>46167</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="AA265" t="inlineStr"/>
       <c r="AB265" t="inlineStr">
@@ -34797,33 +34300,31 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>TF120526</t>
+          <t>TAR260526</t>
         </is>
       </c>
       <c r="T266" s="2" t="n">
-        <v>50</v>
+        <v>11.7</v>
       </c>
       <c r="U266" s="2" t="n">
-        <v>-50</v>
+        <v>-11.7</v>
       </c>
       <c r="V266" s="2" t="n">
-        <v>-50</v>
+        <v>-11.7</v>
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>RENOVACAO CH. ESP. | REFERENTE A TARIFA RENOVAÇÃO DE CHEQUE ESPECIAL G3S 05</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 13 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X266" s="3" t="n">
-        <v>46361</v>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>12/05/26</t>
-        </is>
+        <v>46168</v>
+      </c>
+      <c r="Y266" s="4" t="n">
+        <v>46168</v>
       </c>
       <c r="Z266" s="3" t="n">
-        <v>46361</v>
+        <v>46168</v>
       </c>
       <c r="AA266" t="inlineStr"/>
       <c r="AB266" t="inlineStr">
@@ -34928,38 +34429,36 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>TF150526</t>
+          <t>TAR270526</t>
         </is>
       </c>
       <c r="T267" s="2" t="n">
-        <v>117.85</v>
+        <v>9.9</v>
       </c>
       <c r="U267" s="2" t="n">
-        <v>-117.85</v>
+        <v>-9.9</v>
       </c>
       <c r="V267" s="2" t="n">
-        <v>-117.85</v>
+        <v>-9.9</v>
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>TARIFA PLANO EMPRESARIAL E1 | TARIFA PLANO EMPRESARIAL E1</t>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
         </is>
       </c>
       <c r="X267" s="3" t="n">
-        <v>46157</v>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>15/05/26</t>
-        </is>
+        <v>46169</v>
+      </c>
+      <c r="Y267" s="4" t="n">
+        <v>46169</v>
       </c>
       <c r="Z267" s="3" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="AA267" t="inlineStr"/>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>60746948000112 - BANCO BRADESCO SA</t>
+          <t>5419 - COOPERATIVA SICREDI</t>
         </is>
       </c>
       <c r="AC267" t="inlineStr"/>
@@ -34970,6 +34469,522 @@
       <c r="AH267" t="inlineStr"/>
       <c r="AI267" t="inlineStr"/>
     </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>1.3 BRACOFER</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>1.3.1 PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>7.5.22</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>7.5.22 DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="R268" t="n">
+        <v>3</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>TAR280526</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="U268" s="2" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="V268" s="2" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 11 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="X268" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="Y268" s="4" t="n">
+        <v>46170</v>
+      </c>
+      <c r="Z268" s="3" t="n">
+        <v>46170</v>
+      </c>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>5419 - COOPERATIVA SICREDI</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr"/>
+      <c r="AD268" t="inlineStr"/>
+      <c r="AE268" t="inlineStr"/>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="inlineStr"/>
+      <c r="AH268" t="inlineStr"/>
+      <c r="AI268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>1.3 BRACOFER</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>1.3.1 PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>7.5.22</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>7.5.22 DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="R269" t="n">
+        <v>3</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>TAR290526</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="U269" s="2" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="V269" s="2" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>TARIFA COM R LIQUIDACAO REF A 26 OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="X269" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="Y269" s="4" t="n">
+        <v>46171</v>
+      </c>
+      <c r="Z269" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="AA269" t="inlineStr"/>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>5419 - COOPERATIVA SICREDI</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr"/>
+      <c r="AD269" t="inlineStr"/>
+      <c r="AE269" t="inlineStr"/>
+      <c r="AF269" t="inlineStr"/>
+      <c r="AG269" t="inlineStr"/>
+      <c r="AH269" t="inlineStr"/>
+      <c r="AI269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>1.3 BRACOFER</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>1.3.1 PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>7.5.22</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>7.5.22 DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="R270" t="n">
+        <v>3</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>TF120526</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="U270" s="2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="V270" s="2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>RENOVACAO CH. ESP.</t>
+        </is>
+      </c>
+      <c r="X270" s="3" t="n">
+        <v>46154</v>
+      </c>
+      <c r="Y270" s="4" t="n">
+        <v>46154</v>
+      </c>
+      <c r="Z270" s="3" t="n">
+        <v>46154</v>
+      </c>
+      <c r="AA270" t="inlineStr"/>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>5419 - COOPERATIVA SICREDI</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr"/>
+      <c r="AD270" t="inlineStr"/>
+      <c r="AE270" t="inlineStr"/>
+      <c r="AF270" t="inlineStr"/>
+      <c r="AG270" t="inlineStr"/>
+      <c r="AH270" t="inlineStr"/>
+      <c r="AI270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>BRACOFER</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>1.3 BRACOFER</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>1.3.1 PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>1.3.1.1</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>1.3.1.1 ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>7.5.22</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>7.5.22 DESPESAS BANCARIAS</t>
+        </is>
+      </c>
+      <c r="R271" t="n">
+        <v>3</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>TF150526</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="U271" s="2" t="n">
+        <v>-117.85</v>
+      </c>
+      <c r="V271" s="2" t="n">
+        <v>-117.85</v>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>TARIFA PLANO EMPRESARIAL E1</t>
+        </is>
+      </c>
+      <c r="X271" s="3" t="n">
+        <v>46157</v>
+      </c>
+      <c r="Y271" s="4" t="n">
+        <v>46157</v>
+      </c>
+      <c r="Z271" s="3" t="n">
+        <v>46157</v>
+      </c>
+      <c r="AA271" t="inlineStr"/>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>60746948000112 - BANCO BRADESCO SA</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr"/>
+      <c r="AD271" t="inlineStr"/>
+      <c r="AE271" t="inlineStr"/>
+      <c r="AF271" t="inlineStr"/>
+      <c r="AG271" t="inlineStr"/>
+      <c r="AH271" t="inlineStr"/>
+      <c r="AI271" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
